--- a/outputs/Laporan-Layer-01-06-2026-sd-30-06-2026.xlsx
+++ b/outputs/Laporan-Layer-01-06-2026-sd-30-06-2026.xlsx
@@ -11,10 +11,9 @@
     <sheet name="Telur C4 18" sheetId="2" r:id="rId5"/>
     <sheet name="Telur D3 16" sheetId="3" r:id="rId6"/>
     <sheet name="Telur E2 13" sheetId="4" r:id="rId7"/>
-    <sheet name="Telur F2 20" sheetId="5" r:id="rId8"/>
-    <sheet name="Telur G2 19" sheetId="6" r:id="rId9"/>
-    <sheet name="Telur H1 14" sheetId="7" r:id="rId10"/>
-    <sheet name="Telur I1 15" sheetId="8" r:id="rId11"/>
+    <sheet name="Telur G2 19" sheetId="5" r:id="rId8"/>
+    <sheet name="Telur H1 14" sheetId="6" r:id="rId9"/>
+    <sheet name="Telur I1 15" sheetId="7" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
@@ -22,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="219">
   <si>
     <t>DATA TELUR PERIODE 01/06/2026 - 30/06/2026</t>
   </si>
@@ -643,24 +642,6 @@
   <si>
     <t>7/7
 30/06</t>
-  </si>
-  <si>
-    <t>F2</t>
-  </si>
-  <si>
-    <t>Minggu ke-7</t>
-  </si>
-  <si>
-    <t>Minggu ke-8</t>
-  </si>
-  <si>
-    <t>Minggu ke-9</t>
-  </si>
-  <si>
-    <t>Minggu ke-10</t>
-  </si>
-  <si>
-    <t>Minggu ke-11</t>
   </si>
   <si>
     <t>G2</t>
@@ -1147,7 +1128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="46">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
@@ -1282,12 +1263,6 @@
       <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="6" numFmtId="2" fillId="7" borderId="9" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="6" numFmtId="2" fillId="7" borderId="7" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="6" numFmtId="2" fillId="7" borderId="10" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
   </cellXfs>
@@ -9318,853 +9293,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AF22"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col min="1" max="1" width="24" customWidth="true" style="0"/>
-    <col min="2" max="2" width="3" customWidth="true" style="0"/>
-    <col min="3" max="3" width="11" customWidth="true" style="0"/>
-    <col min="4" max="4" width="11" customWidth="true" style="0"/>
-    <col min="5" max="5" width="11" customWidth="true" style="0"/>
-    <col min="6" max="6" width="11" customWidth="true" style="0"/>
-    <col min="7" max="7" width="11" customWidth="true" style="0"/>
-    <col min="8" max="8" width="11" customWidth="true" style="0"/>
-    <col min="9" max="9" width="11" customWidth="true" style="0"/>
-    <col min="10" max="10" width="11" customWidth="true" style="0"/>
-    <col min="11" max="11" width="11" customWidth="true" style="0"/>
-    <col min="12" max="12" width="11" customWidth="true" style="0"/>
-    <col min="13" max="13" width="11" customWidth="true" style="0"/>
-    <col min="14" max="14" width="11" customWidth="true" style="0"/>
-    <col min="15" max="15" width="11" customWidth="true" style="0"/>
-    <col min="16" max="16" width="11" customWidth="true" style="0"/>
-    <col min="17" max="17" width="11" customWidth="true" style="0"/>
-    <col min="18" max="18" width="11" customWidth="true" style="0"/>
-    <col min="19" max="19" width="11" customWidth="true" style="0"/>
-    <col min="20" max="20" width="11" customWidth="true" style="0"/>
-    <col min="21" max="21" width="11" customWidth="true" style="0"/>
-    <col min="22" max="22" width="11" customWidth="true" style="0"/>
-    <col min="23" max="23" width="11" customWidth="true" style="0"/>
-    <col min="24" max="24" width="11" customWidth="true" style="0"/>
-    <col min="25" max="25" width="11" customWidth="true" style="0"/>
-    <col min="26" max="26" width="11" customWidth="true" style="0"/>
-    <col min="27" max="27" width="11" customWidth="true" style="0"/>
-    <col min="28" max="28" width="11" customWidth="true" style="0"/>
-    <col min="29" max="29" width="11" customWidth="true" style="0"/>
-    <col min="30" max="30" width="11" customWidth="true" style="0"/>
-    <col min="31" max="31" width="11" customWidth="true" style="0"/>
-    <col min="32" max="32" width="11" customWidth="true" style="0"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:32" customHeight="1" ht="28">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
-      <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
-      <c r="W1" s="1"/>
-      <c r="X1" s="1"/>
-      <c r="Y1" s="1"/>
-      <c r="Z1" s="1"/>
-      <c r="AA1" s="1"/>
-      <c r="AB1" s="1"/>
-      <c r="AC1" s="1"/>
-      <c r="AD1" s="1"/>
-      <c r="AE1" s="1"/>
-      <c r="AF1" s="1"/>
-    </row>
-    <row r="2" spans="1:32">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="3" spans="1:32">
-      <c r="A3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="5">
-        <v>46127.0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:32">
-      <c r="A4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:32" customHeight="1" ht="26">
-      <c r="A6" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="8"/>
-      <c r="L6" s="8"/>
-      <c r="M6" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="N6" s="8"/>
-      <c r="O6" s="8"/>
-      <c r="P6" s="8"/>
-      <c r="Q6" s="8"/>
-      <c r="R6" s="8"/>
-      <c r="S6" s="8"/>
-      <c r="T6" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="U6" s="8"/>
-      <c r="V6" s="8"/>
-      <c r="W6" s="8"/>
-      <c r="X6" s="8"/>
-      <c r="Y6" s="8"/>
-      <c r="Z6" s="8"/>
-      <c r="AA6" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="AB6" s="8"/>
-      <c r="AC6" s="8"/>
-      <c r="AD6" s="8"/>
-      <c r="AE6" s="8"/>
-      <c r="AF6" s="11"/>
-    </row>
-    <row r="7" spans="1:32" customHeight="1" ht="36">
-      <c r="A7" s="7"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="H7" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="I7" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="J7" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="K7" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="L7" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="M7" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="N7" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="O7" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="P7" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="Q7" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="R7" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="S7" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="T7" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="U7" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="V7" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="W7" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="X7" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="Y7" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="Z7" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="AA7" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="AB7" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="AC7" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="AD7" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="AE7" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="AF7" s="12" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="8" spans="1:32">
-      <c r="A8" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="19"/>
-      <c r="I8" s="19"/>
-      <c r="J8" s="19"/>
-      <c r="K8" s="19"/>
-      <c r="L8" s="19"/>
-      <c r="M8" s="19"/>
-      <c r="N8" s="19"/>
-      <c r="O8" s="19"/>
-      <c r="P8" s="19"/>
-      <c r="Q8" s="19"/>
-      <c r="R8" s="19"/>
-      <c r="S8" s="19"/>
-      <c r="T8" s="19"/>
-      <c r="U8" s="19"/>
-      <c r="V8" s="19"/>
-      <c r="W8" s="19"/>
-      <c r="X8" s="19"/>
-      <c r="Y8" s="19"/>
-      <c r="Z8" s="19"/>
-      <c r="AA8" s="19"/>
-      <c r="AB8" s="19"/>
-      <c r="AC8" s="19"/>
-      <c r="AD8" s="19"/>
-      <c r="AE8" s="19"/>
-      <c r="AF8" s="32"/>
-    </row>
-    <row r="9" spans="1:32">
-      <c r="A9" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="C9" s="20"/>
-      <c r="D9" s="20"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="20"/>
-      <c r="I9" s="20"/>
-      <c r="J9" s="20"/>
-      <c r="K9" s="20"/>
-      <c r="L9" s="20"/>
-      <c r="M9" s="20"/>
-      <c r="N9" s="20"/>
-      <c r="O9" s="20"/>
-      <c r="P9" s="20"/>
-      <c r="Q9" s="20"/>
-      <c r="R9" s="20"/>
-      <c r="S9" s="20"/>
-      <c r="T9" s="20"/>
-      <c r="U9" s="20"/>
-      <c r="V9" s="20"/>
-      <c r="W9" s="20"/>
-      <c r="X9" s="20"/>
-      <c r="Y9" s="20"/>
-      <c r="Z9" s="20"/>
-      <c r="AA9" s="20"/>
-      <c r="AB9" s="20"/>
-      <c r="AC9" s="20"/>
-      <c r="AD9" s="20"/>
-      <c r="AE9" s="20"/>
-      <c r="AF9" s="33"/>
-    </row>
-    <row r="10" spans="1:32">
-      <c r="A10" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="B10" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="19"/>
-      <c r="F10" s="19"/>
-      <c r="G10" s="19"/>
-      <c r="H10" s="19"/>
-      <c r="I10" s="19"/>
-      <c r="J10" s="19"/>
-      <c r="K10" s="19"/>
-      <c r="L10" s="19"/>
-      <c r="M10" s="19"/>
-      <c r="N10" s="19"/>
-      <c r="O10" s="19"/>
-      <c r="P10" s="19"/>
-      <c r="Q10" s="19"/>
-      <c r="R10" s="19"/>
-      <c r="S10" s="19"/>
-      <c r="T10" s="19"/>
-      <c r="U10" s="19"/>
-      <c r="V10" s="19"/>
-      <c r="W10" s="19"/>
-      <c r="X10" s="19"/>
-      <c r="Y10" s="19"/>
-      <c r="Z10" s="19"/>
-      <c r="AA10" s="19"/>
-      <c r="AB10" s="19"/>
-      <c r="AC10" s="19"/>
-      <c r="AD10" s="19"/>
-      <c r="AE10" s="19"/>
-      <c r="AF10" s="32"/>
-    </row>
-    <row r="11" spans="1:32">
-      <c r="A11" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="B11" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="C11" s="21"/>
-      <c r="D11" s="21"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="21"/>
-      <c r="G11" s="21"/>
-      <c r="H11" s="21"/>
-      <c r="I11" s="21"/>
-      <c r="J11" s="21"/>
-      <c r="K11" s="21"/>
-      <c r="L11" s="21"/>
-      <c r="M11" s="21"/>
-      <c r="N11" s="21"/>
-      <c r="O11" s="21"/>
-      <c r="P11" s="21"/>
-      <c r="Q11" s="21"/>
-      <c r="R11" s="21"/>
-      <c r="S11" s="21"/>
-      <c r="T11" s="21"/>
-      <c r="U11" s="21"/>
-      <c r="V11" s="21"/>
-      <c r="W11" s="21"/>
-      <c r="X11" s="21"/>
-      <c r="Y11" s="21"/>
-      <c r="Z11" s="21"/>
-      <c r="AA11" s="21"/>
-      <c r="AB11" s="21"/>
-      <c r="AC11" s="21"/>
-      <c r="AD11" s="21"/>
-      <c r="AE11" s="21"/>
-      <c r="AF11" s="34"/>
-    </row>
-    <row r="12" spans="1:32">
-      <c r="A12" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="B12" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="C12" s="22"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="22"/>
-      <c r="G12" s="22"/>
-      <c r="H12" s="22"/>
-      <c r="I12" s="22"/>
-      <c r="J12" s="22"/>
-      <c r="K12" s="22"/>
-      <c r="L12" s="22"/>
-      <c r="M12" s="22"/>
-      <c r="N12" s="22"/>
-      <c r="O12" s="22"/>
-      <c r="P12" s="22"/>
-      <c r="Q12" s="22"/>
-      <c r="R12" s="22"/>
-      <c r="S12" s="22"/>
-      <c r="T12" s="22"/>
-      <c r="U12" s="22"/>
-      <c r="V12" s="22"/>
-      <c r="W12" s="22"/>
-      <c r="X12" s="22"/>
-      <c r="Y12" s="22"/>
-      <c r="Z12" s="22"/>
-      <c r="AA12" s="22"/>
-      <c r="AB12" s="22"/>
-      <c r="AC12" s="22"/>
-      <c r="AD12" s="22"/>
-      <c r="AE12" s="22"/>
-      <c r="AF12" s="35"/>
-    </row>
-    <row r="13" spans="1:32">
-      <c r="A13" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="B13" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="C13" s="23"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="23"/>
-      <c r="G13" s="23"/>
-      <c r="H13" s="23"/>
-      <c r="I13" s="23"/>
-      <c r="J13" s="23"/>
-      <c r="K13" s="23"/>
-      <c r="L13" s="23"/>
-      <c r="M13" s="23"/>
-      <c r="N13" s="23"/>
-      <c r="O13" s="23"/>
-      <c r="P13" s="23"/>
-      <c r="Q13" s="23"/>
-      <c r="R13" s="23"/>
-      <c r="S13" s="23"/>
-      <c r="T13" s="23"/>
-      <c r="U13" s="23"/>
-      <c r="V13" s="23"/>
-      <c r="W13" s="23"/>
-      <c r="X13" s="23"/>
-      <c r="Y13" s="23"/>
-      <c r="Z13" s="23"/>
-      <c r="AA13" s="23"/>
-      <c r="AB13" s="23"/>
-      <c r="AC13" s="23"/>
-      <c r="AD13" s="23"/>
-      <c r="AE13" s="23"/>
-      <c r="AF13" s="36"/>
-    </row>
-    <row r="14" spans="1:32">
-      <c r="A14" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="B14" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="C14" s="24"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="24"/>
-      <c r="F14" s="24"/>
-      <c r="G14" s="24"/>
-      <c r="H14" s="24"/>
-      <c r="I14" s="24"/>
-      <c r="J14" s="24"/>
-      <c r="K14" s="24"/>
-      <c r="L14" s="24"/>
-      <c r="M14" s="24"/>
-      <c r="N14" s="24"/>
-      <c r="O14" s="24"/>
-      <c r="P14" s="24"/>
-      <c r="Q14" s="24"/>
-      <c r="R14" s="24"/>
-      <c r="S14" s="24"/>
-      <c r="T14" s="24"/>
-      <c r="U14" s="24"/>
-      <c r="V14" s="24"/>
-      <c r="W14" s="24"/>
-      <c r="X14" s="24"/>
-      <c r="Y14" s="24"/>
-      <c r="Z14" s="24"/>
-      <c r="AA14" s="24"/>
-      <c r="AB14" s="24"/>
-      <c r="AC14" s="24"/>
-      <c r="AD14" s="24"/>
-      <c r="AE14" s="24"/>
-      <c r="AF14" s="37"/>
-    </row>
-    <row r="15" spans="1:32">
-      <c r="A15" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="B15" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="C15" s="25"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="25"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="25"/>
-      <c r="I15" s="25"/>
-      <c r="J15" s="25"/>
-      <c r="K15" s="25"/>
-      <c r="L15" s="25"/>
-      <c r="M15" s="25"/>
-      <c r="N15" s="25"/>
-      <c r="O15" s="25"/>
-      <c r="P15" s="25"/>
-      <c r="Q15" s="25"/>
-      <c r="R15" s="25"/>
-      <c r="S15" s="25"/>
-      <c r="T15" s="25"/>
-      <c r="U15" s="25"/>
-      <c r="V15" s="25"/>
-      <c r="W15" s="25"/>
-      <c r="X15" s="25"/>
-      <c r="Y15" s="25"/>
-      <c r="Z15" s="25"/>
-      <c r="AA15" s="25"/>
-      <c r="AB15" s="25"/>
-      <c r="AC15" s="25"/>
-      <c r="AD15" s="25"/>
-      <c r="AE15" s="25"/>
-      <c r="AF15" s="38"/>
-    </row>
-    <row r="16" spans="1:32">
-      <c r="A16" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="B16" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="C16" s="26"/>
-      <c r="D16" s="26"/>
-      <c r="E16" s="26"/>
-      <c r="F16" s="26"/>
-      <c r="G16" s="26"/>
-      <c r="H16" s="26"/>
-      <c r="I16" s="26"/>
-      <c r="J16" s="26"/>
-      <c r="K16" s="26"/>
-      <c r="L16" s="26"/>
-      <c r="M16" s="26"/>
-      <c r="N16" s="26"/>
-      <c r="O16" s="26"/>
-      <c r="P16" s="26"/>
-      <c r="Q16" s="26"/>
-      <c r="R16" s="26"/>
-      <c r="S16" s="26"/>
-      <c r="T16" s="26"/>
-      <c r="U16" s="26"/>
-      <c r="V16" s="26"/>
-      <c r="W16" s="26"/>
-      <c r="X16" s="26"/>
-      <c r="Y16" s="26"/>
-      <c r="Z16" s="26"/>
-      <c r="AA16" s="26"/>
-      <c r="AB16" s="26"/>
-      <c r="AC16" s="26"/>
-      <c r="AD16" s="26"/>
-      <c r="AE16" s="26"/>
-      <c r="AF16" s="39"/>
-    </row>
-    <row r="17" spans="1:32">
-      <c r="A17" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="B17" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="C17" s="30"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="30"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="30"/>
-      <c r="H17" s="30"/>
-      <c r="I17" s="30"/>
-      <c r="J17" s="30"/>
-      <c r="K17" s="30"/>
-      <c r="L17" s="30"/>
-      <c r="M17" s="30"/>
-      <c r="N17" s="30"/>
-      <c r="O17" s="30"/>
-      <c r="P17" s="30"/>
-      <c r="Q17" s="30"/>
-      <c r="R17" s="30"/>
-      <c r="S17" s="30"/>
-      <c r="T17" s="30"/>
-      <c r="U17" s="30"/>
-      <c r="V17" s="30"/>
-      <c r="W17" s="30"/>
-      <c r="X17" s="30"/>
-      <c r="Y17" s="30"/>
-      <c r="Z17" s="30"/>
-      <c r="AA17" s="30"/>
-      <c r="AB17" s="30"/>
-      <c r="AC17" s="30"/>
-      <c r="AD17" s="30"/>
-      <c r="AE17" s="30"/>
-      <c r="AF17" s="44"/>
-    </row>
-    <row r="18" spans="1:32">
-      <c r="A18" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="B18" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="C18" s="31"/>
-      <c r="D18" s="31"/>
-      <c r="E18" s="31"/>
-      <c r="F18" s="31"/>
-      <c r="G18" s="31"/>
-      <c r="H18" s="31"/>
-      <c r="I18" s="31"/>
-      <c r="J18" s="31"/>
-      <c r="K18" s="31"/>
-      <c r="L18" s="31"/>
-      <c r="M18" s="31"/>
-      <c r="N18" s="31"/>
-      <c r="O18" s="31"/>
-      <c r="P18" s="31"/>
-      <c r="Q18" s="31"/>
-      <c r="R18" s="31"/>
-      <c r="S18" s="31"/>
-      <c r="T18" s="31"/>
-      <c r="U18" s="31"/>
-      <c r="V18" s="31"/>
-      <c r="W18" s="31"/>
-      <c r="X18" s="31"/>
-      <c r="Y18" s="31"/>
-      <c r="Z18" s="31"/>
-      <c r="AA18" s="31"/>
-      <c r="AB18" s="31"/>
-      <c r="AC18" s="31"/>
-      <c r="AD18" s="31"/>
-      <c r="AE18" s="31"/>
-      <c r="AF18" s="46"/>
-    </row>
-    <row r="19" spans="1:32">
-      <c r="A19" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="B19" s="17"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="17"/>
-      <c r="H19" s="17"/>
-      <c r="I19" s="17"/>
-      <c r="J19" s="17"/>
-      <c r="K19" s="17"/>
-      <c r="L19" s="17"/>
-      <c r="M19" s="17"/>
-      <c r="N19" s="17"/>
-      <c r="O19" s="17"/>
-      <c r="P19" s="17"/>
-      <c r="Q19" s="17"/>
-      <c r="R19" s="17"/>
-      <c r="S19" s="17"/>
-      <c r="T19" s="17"/>
-      <c r="U19" s="17"/>
-      <c r="V19" s="17"/>
-      <c r="W19" s="17"/>
-      <c r="X19" s="17"/>
-      <c r="Y19" s="17"/>
-      <c r="Z19" s="17"/>
-      <c r="AA19" s="17"/>
-      <c r="AB19" s="17"/>
-      <c r="AC19" s="17"/>
-      <c r="AD19" s="17"/>
-      <c r="AE19" s="17"/>
-      <c r="AF19" s="42"/>
-    </row>
-    <row r="20" spans="1:32">
-      <c r="A20" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="B20" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="C20" s="24"/>
-      <c r="D20" s="24"/>
-      <c r="E20" s="24"/>
-      <c r="F20" s="24"/>
-      <c r="G20" s="24"/>
-      <c r="H20" s="24"/>
-      <c r="I20" s="24"/>
-      <c r="J20" s="24"/>
-      <c r="K20" s="24"/>
-      <c r="L20" s="24"/>
-      <c r="M20" s="24"/>
-      <c r="N20" s="24"/>
-      <c r="O20" s="24"/>
-      <c r="P20" s="24"/>
-      <c r="Q20" s="24"/>
-      <c r="R20" s="24"/>
-      <c r="S20" s="24"/>
-      <c r="T20" s="24"/>
-      <c r="U20" s="24"/>
-      <c r="V20" s="24"/>
-      <c r="W20" s="24"/>
-      <c r="X20" s="24"/>
-      <c r="Y20" s="24"/>
-      <c r="Z20" s="24"/>
-      <c r="AA20" s="24"/>
-      <c r="AB20" s="24"/>
-      <c r="AC20" s="24"/>
-      <c r="AD20" s="24"/>
-      <c r="AE20" s="24"/>
-      <c r="AF20" s="37"/>
-    </row>
-    <row r="21" spans="1:32">
-      <c r="A21" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="B21" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="C21" s="30"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="30"/>
-      <c r="F21" s="30"/>
-      <c r="G21" s="30"/>
-      <c r="H21" s="30"/>
-      <c r="I21" s="30"/>
-      <c r="J21" s="30"/>
-      <c r="K21" s="30"/>
-      <c r="L21" s="30"/>
-      <c r="M21" s="30"/>
-      <c r="N21" s="30"/>
-      <c r="O21" s="30"/>
-      <c r="P21" s="30"/>
-      <c r="Q21" s="30"/>
-      <c r="R21" s="30"/>
-      <c r="S21" s="30"/>
-      <c r="T21" s="30"/>
-      <c r="U21" s="30"/>
-      <c r="V21" s="30"/>
-      <c r="W21" s="30"/>
-      <c r="X21" s="30"/>
-      <c r="Y21" s="30"/>
-      <c r="Z21" s="30"/>
-      <c r="AA21" s="30"/>
-      <c r="AB21" s="30"/>
-      <c r="AC21" s="30"/>
-      <c r="AD21" s="30"/>
-      <c r="AE21" s="30"/>
-      <c r="AF21" s="44"/>
-    </row>
-    <row r="22" spans="1:32">
-      <c r="A22" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="B22" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="C22" s="45"/>
-      <c r="D22" s="45"/>
-      <c r="E22" s="45"/>
-      <c r="F22" s="45"/>
-      <c r="G22" s="45"/>
-      <c r="H22" s="45"/>
-      <c r="I22" s="45"/>
-      <c r="J22" s="45"/>
-      <c r="K22" s="45"/>
-      <c r="L22" s="45"/>
-      <c r="M22" s="45"/>
-      <c r="N22" s="45"/>
-      <c r="O22" s="45"/>
-      <c r="P22" s="45"/>
-      <c r="Q22" s="45"/>
-      <c r="R22" s="45"/>
-      <c r="S22" s="45"/>
-      <c r="T22" s="45"/>
-      <c r="U22" s="45"/>
-      <c r="V22" s="45"/>
-      <c r="W22" s="45"/>
-      <c r="X22" s="45"/>
-      <c r="Y22" s="45"/>
-      <c r="Z22" s="45"/>
-      <c r="AA22" s="45"/>
-      <c r="AB22" s="45"/>
-      <c r="AC22" s="45"/>
-      <c r="AD22" s="45"/>
-      <c r="AE22" s="45"/>
-      <c r="AF22" s="47"/>
-    </row>
-  </sheetData>
-  <mergeCells>
-    <mergeCell ref="A1:AF1"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="F6:L6"/>
-    <mergeCell ref="M6:S6"/>
-    <mergeCell ref="T6:Z6"/>
-    <mergeCell ref="AA6:AF6"/>
-    <mergeCell ref="A19:AF19"/>
-  </mergeCells>
-  <printOptions gridLines="false" gridLinesSet="true"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="landscape" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <tableParts count="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
   <dimension ref="A1:AF28"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -10246,7 +9374,7 @@
         <v>2</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:32">
@@ -10279,11 +9407,11 @@
         <v>2</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="D6" s="8"/>
       <c r="E6" s="8" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
@@ -10292,7 +9420,7 @@
       <c r="J6" s="8"/>
       <c r="K6" s="8"/>
       <c r="L6" s="8" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="M6" s="8"/>
       <c r="N6" s="8"/>
@@ -10301,7 +9429,7 @@
       <c r="Q6" s="8"/>
       <c r="R6" s="8"/>
       <c r="S6" s="8" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="T6" s="8"/>
       <c r="U6" s="8"/>
@@ -10310,7 +9438,7 @@
       <c r="X6" s="8"/>
       <c r="Y6" s="8"/>
       <c r="Z6" s="8" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="AA6" s="8"/>
       <c r="AB6" s="8"/>
@@ -11373,7 +10501,7 @@
     </row>
     <row r="21" spans="1:32">
       <c r="A21" s="13" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="B21" s="16" t="s">
         <v>2</v>
@@ -11455,7 +10583,7 @@
     </row>
     <row r="22" spans="1:32">
       <c r="A22" s="13" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="B22" s="16" t="s">
         <v>2</v>
@@ -11996,6 +11124,1938 @@
     <mergeCell ref="S6:Y6"/>
     <mergeCell ref="Z6:AF6"/>
     <mergeCell ref="A25:AF25"/>
+  </mergeCells>
+  <printOptions gridLines="false" gridLinesSet="true"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="landscape" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver"/>
+  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
+    <oddHeader/>
+    <oddFooter/>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <tableParts count="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:AF26"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col min="1" max="1" width="24" customWidth="true" style="0"/>
+    <col min="2" max="2" width="3" customWidth="true" style="0"/>
+    <col min="3" max="3" width="11" customWidth="true" style="0"/>
+    <col min="4" max="4" width="11" customWidth="true" style="0"/>
+    <col min="5" max="5" width="11" customWidth="true" style="0"/>
+    <col min="6" max="6" width="11" customWidth="true" style="0"/>
+    <col min="7" max="7" width="11" customWidth="true" style="0"/>
+    <col min="8" max="8" width="11" customWidth="true" style="0"/>
+    <col min="9" max="9" width="11" customWidth="true" style="0"/>
+    <col min="10" max="10" width="11" customWidth="true" style="0"/>
+    <col min="11" max="11" width="11" customWidth="true" style="0"/>
+    <col min="12" max="12" width="11" customWidth="true" style="0"/>
+    <col min="13" max="13" width="11" customWidth="true" style="0"/>
+    <col min="14" max="14" width="11" customWidth="true" style="0"/>
+    <col min="15" max="15" width="11" customWidth="true" style="0"/>
+    <col min="16" max="16" width="11" customWidth="true" style="0"/>
+    <col min="17" max="17" width="11" customWidth="true" style="0"/>
+    <col min="18" max="18" width="11" customWidth="true" style="0"/>
+    <col min="19" max="19" width="11" customWidth="true" style="0"/>
+    <col min="20" max="20" width="11" customWidth="true" style="0"/>
+    <col min="21" max="21" width="11" customWidth="true" style="0"/>
+    <col min="22" max="22" width="11" customWidth="true" style="0"/>
+    <col min="23" max="23" width="11" customWidth="true" style="0"/>
+    <col min="24" max="24" width="11" customWidth="true" style="0"/>
+    <col min="25" max="25" width="11" customWidth="true" style="0"/>
+    <col min="26" max="26" width="11" customWidth="true" style="0"/>
+    <col min="27" max="27" width="11" customWidth="true" style="0"/>
+    <col min="28" max="28" width="11" customWidth="true" style="0"/>
+    <col min="29" max="29" width="11" customWidth="true" style="0"/>
+    <col min="30" max="30" width="11" customWidth="true" style="0"/>
+    <col min="31" max="31" width="11" customWidth="true" style="0"/>
+    <col min="32" max="32" width="11" customWidth="true" style="0"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:32" customHeight="1" ht="28">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
+      <c r="V1" s="1"/>
+      <c r="W1" s="1"/>
+      <c r="X1" s="1"/>
+      <c r="Y1" s="1"/>
+      <c r="Z1" s="1"/>
+      <c r="AA1" s="1"/>
+      <c r="AB1" s="1"/>
+      <c r="AC1" s="1"/>
+      <c r="AD1" s="1"/>
+      <c r="AE1" s="1"/>
+      <c r="AF1" s="1"/>
+    </row>
+    <row r="2" spans="1:32">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32">
+      <c r="A3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="5">
+        <v>45775.0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32">
+      <c r="A4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" customHeight="1" ht="26">
+      <c r="A6" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="L6" s="8"/>
+      <c r="M6" s="8"/>
+      <c r="N6" s="8"/>
+      <c r="O6" s="8"/>
+      <c r="P6" s="8"/>
+      <c r="Q6" s="8"/>
+      <c r="R6" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="S6" s="8"/>
+      <c r="T6" s="8"/>
+      <c r="U6" s="8"/>
+      <c r="V6" s="8"/>
+      <c r="W6" s="8"/>
+      <c r="X6" s="8"/>
+      <c r="Y6" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="Z6" s="8"/>
+      <c r="AA6" s="8"/>
+      <c r="AB6" s="8"/>
+      <c r="AC6" s="8"/>
+      <c r="AD6" s="8"/>
+      <c r="AE6" s="8"/>
+      <c r="AF6" s="11" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" customHeight="1" ht="36">
+      <c r="A7" s="7"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="K7" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="L7" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="M7" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="N7" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="O7" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="P7" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="Q7" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="R7" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="S7" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="T7" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="U7" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="V7" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="W7" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="X7" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="Y7" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="Z7" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="AA7" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="AB7" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="AC7" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="AD7" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="AE7" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="AF7" s="12" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32">
+      <c r="A8" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="19">
+        <v>5.0</v>
+      </c>
+      <c r="D8" s="19">
+        <v>1.0</v>
+      </c>
+      <c r="E8" s="19">
+        <v>2.0</v>
+      </c>
+      <c r="F8" s="19">
+        <v>4.0</v>
+      </c>
+      <c r="G8" s="19">
+        <v>3.0</v>
+      </c>
+      <c r="H8" s="19">
+        <v>3.0</v>
+      </c>
+      <c r="I8" s="19">
+        <v>3.0</v>
+      </c>
+      <c r="J8" s="19">
+        <v>3.0</v>
+      </c>
+      <c r="K8" s="19">
+        <v>3.0</v>
+      </c>
+      <c r="L8" s="19">
+        <v>3.0</v>
+      </c>
+      <c r="M8" s="19">
+        <v>2.0</v>
+      </c>
+      <c r="N8" s="19">
+        <v>3.0</v>
+      </c>
+      <c r="O8" s="19"/>
+      <c r="P8" s="19">
+        <v>6.0</v>
+      </c>
+      <c r="Q8" s="19"/>
+      <c r="R8" s="19">
+        <v>3.0</v>
+      </c>
+      <c r="S8" s="19">
+        <v>1.0</v>
+      </c>
+      <c r="T8" s="19">
+        <v>4.0</v>
+      </c>
+      <c r="U8" s="19">
+        <v>1.0</v>
+      </c>
+      <c r="V8" s="19"/>
+      <c r="W8" s="19">
+        <v>2.0</v>
+      </c>
+      <c r="X8" s="19">
+        <v>1.0</v>
+      </c>
+      <c r="Y8" s="19">
+        <v>2.0</v>
+      </c>
+      <c r="Z8" s="19">
+        <v>3.0</v>
+      </c>
+      <c r="AA8" s="19">
+        <v>2.0</v>
+      </c>
+      <c r="AB8" s="19">
+        <v>2.0</v>
+      </c>
+      <c r="AC8" s="19">
+        <v>2.0</v>
+      </c>
+      <c r="AD8" s="19">
+        <v>3.0</v>
+      </c>
+      <c r="AE8" s="19">
+        <v>3.0</v>
+      </c>
+      <c r="AF8" s="32">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32">
+      <c r="A9" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="20"/>
+      <c r="I9" s="20"/>
+      <c r="J9" s="20"/>
+      <c r="K9" s="20"/>
+      <c r="L9" s="20"/>
+      <c r="M9" s="20"/>
+      <c r="N9" s="20"/>
+      <c r="O9" s="20"/>
+      <c r="P9" s="20"/>
+      <c r="Q9" s="20"/>
+      <c r="R9" s="20"/>
+      <c r="S9" s="20"/>
+      <c r="T9" s="20"/>
+      <c r="U9" s="20"/>
+      <c r="V9" s="20"/>
+      <c r="W9" s="20"/>
+      <c r="X9" s="20"/>
+      <c r="Y9" s="20"/>
+      <c r="Z9" s="20"/>
+      <c r="AA9" s="20"/>
+      <c r="AB9" s="20"/>
+      <c r="AC9" s="20"/>
+      <c r="AD9" s="20"/>
+      <c r="AE9" s="20"/>
+      <c r="AF9" s="33"/>
+    </row>
+    <row r="10" spans="1:32">
+      <c r="A10" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="C10" s="19">
+        <v>6224.0</v>
+      </c>
+      <c r="D10" s="19">
+        <v>6142.0</v>
+      </c>
+      <c r="E10" s="19">
+        <v>6153.0</v>
+      </c>
+      <c r="F10" s="19">
+        <v>6163.0</v>
+      </c>
+      <c r="G10" s="19">
+        <v>6173.0</v>
+      </c>
+      <c r="H10" s="19">
+        <v>5966.0</v>
+      </c>
+      <c r="I10" s="19">
+        <v>5969.0</v>
+      </c>
+      <c r="J10" s="19">
+        <v>6004.0</v>
+      </c>
+      <c r="K10" s="19">
+        <v>6021.0</v>
+      </c>
+      <c r="L10" s="19">
+        <v>5990.0</v>
+      </c>
+      <c r="M10" s="19">
+        <v>5852.0</v>
+      </c>
+      <c r="N10" s="19">
+        <v>5786.0</v>
+      </c>
+      <c r="O10" s="19">
+        <v>5715.0</v>
+      </c>
+      <c r="P10" s="19">
+        <v>5842.0</v>
+      </c>
+      <c r="Q10" s="19">
+        <v>6009.0</v>
+      </c>
+      <c r="R10" s="19">
+        <v>6079.0</v>
+      </c>
+      <c r="S10" s="19">
+        <v>6124.0</v>
+      </c>
+      <c r="T10" s="19">
+        <v>5969.0</v>
+      </c>
+      <c r="U10" s="19">
+        <v>6177.0</v>
+      </c>
+      <c r="V10" s="19">
+        <v>6287.0</v>
+      </c>
+      <c r="W10" s="19">
+        <v>6290.0</v>
+      </c>
+      <c r="X10" s="19">
+        <v>6313.0</v>
+      </c>
+      <c r="Y10" s="19">
+        <v>6224.0</v>
+      </c>
+      <c r="Z10" s="19">
+        <v>6105.0</v>
+      </c>
+      <c r="AA10" s="19">
+        <v>6045.0</v>
+      </c>
+      <c r="AB10" s="19">
+        <v>5943.0</v>
+      </c>
+      <c r="AC10" s="19">
+        <v>5682.0</v>
+      </c>
+      <c r="AD10" s="19">
+        <v>5776.0</v>
+      </c>
+      <c r="AE10" s="19">
+        <v>5840.0</v>
+      </c>
+      <c r="AF10" s="32">
+        <v>5948.0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32">
+      <c r="A11" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="C11" s="21">
+        <v>393.52222222222</v>
+      </c>
+      <c r="D11" s="21">
+        <v>387.17777777778</v>
+      </c>
+      <c r="E11" s="21">
+        <v>391.81666666667</v>
+      </c>
+      <c r="F11" s="21">
+        <v>394.86111111111</v>
+      </c>
+      <c r="G11" s="21">
+        <v>390.80555555556</v>
+      </c>
+      <c r="H11" s="21">
+        <v>376.25555555556</v>
+      </c>
+      <c r="I11" s="21">
+        <v>376.13888888889</v>
+      </c>
+      <c r="J11" s="21">
+        <v>378.24444444444</v>
+      </c>
+      <c r="K11" s="21">
+        <v>382.35</v>
+      </c>
+      <c r="L11" s="21">
+        <v>382.12222222222</v>
+      </c>
+      <c r="M11" s="21">
+        <v>372.38888888889</v>
+      </c>
+      <c r="N11" s="21">
+        <v>375.15555555556</v>
+      </c>
+      <c r="O11" s="21">
+        <v>361.95</v>
+      </c>
+      <c r="P11" s="21">
+        <v>370.54444444444</v>
+      </c>
+      <c r="Q11" s="21">
+        <v>382.61666666667</v>
+      </c>
+      <c r="R11" s="21">
+        <v>387.12777777778</v>
+      </c>
+      <c r="S11" s="21">
+        <v>392.27777777778</v>
+      </c>
+      <c r="T11" s="21">
+        <v>381.33888888889</v>
+      </c>
+      <c r="U11" s="21">
+        <v>394.68333333333</v>
+      </c>
+      <c r="V11" s="21">
+        <v>403.87222222222</v>
+      </c>
+      <c r="W11" s="21">
+        <v>403.85555555556</v>
+      </c>
+      <c r="X11" s="21">
+        <v>402.02777777778</v>
+      </c>
+      <c r="Y11" s="21">
+        <v>392.92222222222</v>
+      </c>
+      <c r="Z11" s="21">
+        <v>389.68333333333</v>
+      </c>
+      <c r="AA11" s="21">
+        <v>383.31666666667</v>
+      </c>
+      <c r="AB11" s="21">
+        <v>376.78333333333</v>
+      </c>
+      <c r="AC11" s="21">
+        <v>358.43333333333</v>
+      </c>
+      <c r="AD11" s="21">
+        <v>365.81111111111</v>
+      </c>
+      <c r="AE11" s="21">
+        <v>368.25555555556</v>
+      </c>
+      <c r="AF11" s="34">
+        <v>371.15555555556</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32">
+      <c r="A12" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" s="22">
+        <v>63.226578120537</v>
+      </c>
+      <c r="D12" s="22">
+        <v>63.037736531712</v>
+      </c>
+      <c r="E12" s="22">
+        <v>63.67896419091</v>
+      </c>
+      <c r="F12" s="22">
+        <v>64.069626985415</v>
+      </c>
+      <c r="G12" s="22">
+        <v>63.308853969797</v>
+      </c>
+      <c r="H12" s="22">
+        <v>63.066636868179</v>
+      </c>
+      <c r="I12" s="22">
+        <v>63.015394352302</v>
+      </c>
+      <c r="J12" s="22">
+        <v>62.998741579688</v>
+      </c>
+      <c r="K12" s="22">
+        <v>63.50274040857</v>
+      </c>
+      <c r="L12" s="22">
+        <v>63.793359302541</v>
+      </c>
+      <c r="M12" s="22">
+        <v>63.634464950254</v>
+      </c>
+      <c r="N12" s="22">
+        <v>64.838499059031</v>
+      </c>
+      <c r="O12" s="22">
+        <v>63.333333333333</v>
+      </c>
+      <c r="P12" s="22">
+        <v>63.427669367416</v>
+      </c>
+      <c r="Q12" s="22">
+        <v>63.673933544128</v>
+      </c>
+      <c r="R12" s="22">
+        <v>63.682806017072</v>
+      </c>
+      <c r="S12" s="22">
+        <v>64.05580956528</v>
+      </c>
+      <c r="T12" s="22">
+        <v>63.886562052084</v>
+      </c>
+      <c r="U12" s="22">
+        <v>63.895634342453</v>
+      </c>
+      <c r="V12" s="22">
+        <v>64.239259141438</v>
+      </c>
+      <c r="W12" s="22">
+        <v>64.205970676559</v>
+      </c>
+      <c r="X12" s="22">
+        <v>63.682524596512</v>
+      </c>
+      <c r="Y12" s="22">
+        <v>63.130177092259</v>
+      </c>
+      <c r="Z12" s="22">
+        <v>63.830193830194</v>
+      </c>
+      <c r="AA12" s="22">
+        <v>63.41053212021</v>
+      </c>
+      <c r="AB12" s="22">
+        <v>63.3995176398</v>
+      </c>
+      <c r="AC12" s="22">
+        <v>63.08224803473</v>
+      </c>
+      <c r="AD12" s="22">
+        <v>63.332948599569</v>
+      </c>
+      <c r="AE12" s="22">
+        <v>63.057458143075</v>
+      </c>
+      <c r="AF12" s="35">
+        <v>62.400059777329</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32">
+      <c r="A13" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="C13" s="23">
+        <v>63.8</v>
+      </c>
+      <c r="D13" s="23">
+        <v>63.9</v>
+      </c>
+      <c r="E13" s="23">
+        <v>63.9</v>
+      </c>
+      <c r="F13" s="23">
+        <v>63.9</v>
+      </c>
+      <c r="G13" s="23">
+        <v>63.9</v>
+      </c>
+      <c r="H13" s="23">
+        <v>63.9</v>
+      </c>
+      <c r="I13" s="23">
+        <v>63.9</v>
+      </c>
+      <c r="J13" s="23">
+        <v>63.9</v>
+      </c>
+      <c r="K13" s="23">
+        <v>63.9</v>
+      </c>
+      <c r="L13" s="23">
+        <v>63.9</v>
+      </c>
+      <c r="M13" s="23">
+        <v>63.9</v>
+      </c>
+      <c r="N13" s="23">
+        <v>63.9</v>
+      </c>
+      <c r="O13" s="23">
+        <v>63.9</v>
+      </c>
+      <c r="P13" s="23">
+        <v>63.9</v>
+      </c>
+      <c r="Q13" s="23">
+        <v>63.9</v>
+      </c>
+      <c r="R13" s="23">
+        <v>63.9</v>
+      </c>
+      <c r="S13" s="23">
+        <v>63.9</v>
+      </c>
+      <c r="T13" s="23">
+        <v>63.9</v>
+      </c>
+      <c r="U13" s="23">
+        <v>63.9</v>
+      </c>
+      <c r="V13" s="23">
+        <v>63.9</v>
+      </c>
+      <c r="W13" s="23">
+        <v>63.9</v>
+      </c>
+      <c r="X13" s="23">
+        <v>63.9</v>
+      </c>
+      <c r="Y13" s="23">
+        <v>63.9</v>
+      </c>
+      <c r="Z13" s="23">
+        <v>63.9</v>
+      </c>
+      <c r="AA13" s="23">
+        <v>63.9</v>
+      </c>
+      <c r="AB13" s="23">
+        <v>63.9</v>
+      </c>
+      <c r="AC13" s="23">
+        <v>63.9</v>
+      </c>
+      <c r="AD13" s="23">
+        <v>63.9</v>
+      </c>
+      <c r="AE13" s="23">
+        <v>63.9</v>
+      </c>
+      <c r="AF13" s="36">
+        <v>64.0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32">
+      <c r="A14" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="24">
+        <v>85.871964679912</v>
+      </c>
+      <c r="D14" s="24">
+        <v>84.752311301228</v>
+      </c>
+      <c r="E14" s="24">
+        <v>84.950987160017</v>
+      </c>
+      <c r="F14" s="24">
+        <v>85.136068517751</v>
+      </c>
+      <c r="G14" s="24">
+        <v>85.309563294638</v>
+      </c>
+      <c r="H14" s="24">
+        <v>82.483063735656</v>
+      </c>
+      <c r="I14" s="24">
+        <v>82.581627006087</v>
+      </c>
+      <c r="J14" s="24">
+        <v>83.134865688175</v>
+      </c>
+      <c r="K14" s="24">
+        <v>83.404903726278</v>
+      </c>
+      <c r="L14" s="24">
+        <v>83.021483021483</v>
+      </c>
+      <c r="M14" s="24">
+        <v>81.13129072508</v>
+      </c>
+      <c r="N14" s="24">
+        <v>80.249653259362</v>
+      </c>
+      <c r="O14" s="24">
+        <v>79.264909847434</v>
+      </c>
+      <c r="P14" s="24">
+        <v>81.093836757357</v>
+      </c>
+      <c r="Q14" s="24">
+        <v>83.411993337035</v>
+      </c>
+      <c r="R14" s="24">
+        <v>84.418830717956</v>
+      </c>
+      <c r="S14" s="24">
+        <v>85.055555555556</v>
+      </c>
+      <c r="T14" s="24">
+        <v>82.948860478043</v>
+      </c>
+      <c r="U14" s="24">
+        <v>85.85128561501</v>
+      </c>
+      <c r="V14" s="24">
+        <v>87.380125086866</v>
+      </c>
+      <c r="W14" s="24">
+        <v>87.446128180175</v>
+      </c>
+      <c r="X14" s="24">
+        <v>87.77808676307</v>
+      </c>
+      <c r="Y14" s="24">
+        <v>86.588759042849</v>
+      </c>
+      <c r="Z14" s="24">
+        <v>84.968684759916</v>
+      </c>
+      <c r="AA14" s="24">
+        <v>84.168755221387</v>
+      </c>
+      <c r="AB14" s="24">
+        <v>82.794650320424</v>
+      </c>
+      <c r="AC14" s="24">
+        <v>79.213718109578</v>
+      </c>
+      <c r="AD14" s="24">
+        <v>80.569117031664</v>
+      </c>
+      <c r="AE14" s="24">
+        <v>81.495953111917</v>
+      </c>
+      <c r="AF14" s="37">
+        <v>83.072625698324</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32">
+      <c r="A15" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="C15" s="25">
+        <v>85.267795676718</v>
+      </c>
+      <c r="D15" s="25">
+        <v>84.974521415783</v>
+      </c>
+      <c r="E15" s="25">
+        <v>85.289256198347</v>
+      </c>
+      <c r="F15" s="25">
+        <v>85.163245626119</v>
+      </c>
+      <c r="G15" s="25">
+        <v>85.804851157663</v>
+      </c>
+      <c r="H15" s="25">
+        <v>85.732009925558</v>
+      </c>
+      <c r="I15" s="25">
+        <v>85.219909003171</v>
+      </c>
+      <c r="J15" s="25">
+        <v>85.871964679912</v>
+      </c>
+      <c r="K15" s="25">
+        <v>84.752311301228</v>
+      </c>
+      <c r="L15" s="25">
+        <v>84.950987160017</v>
+      </c>
+      <c r="M15" s="25">
+        <v>85.136068517751</v>
+      </c>
+      <c r="N15" s="25">
+        <v>85.309563294638</v>
+      </c>
+      <c r="O15" s="25">
+        <v>82.483063735656</v>
+      </c>
+      <c r="P15" s="25">
+        <v>82.581627006087</v>
+      </c>
+      <c r="Q15" s="25">
+        <v>83.134865688175</v>
+      </c>
+      <c r="R15" s="25">
+        <v>83.404903726278</v>
+      </c>
+      <c r="S15" s="25">
+        <v>83.021483021483</v>
+      </c>
+      <c r="T15" s="25">
+        <v>81.13129072508</v>
+      </c>
+      <c r="U15" s="25">
+        <v>80.249653259362</v>
+      </c>
+      <c r="V15" s="25">
+        <v>79.264909847434</v>
+      </c>
+      <c r="W15" s="25">
+        <v>81.093836757357</v>
+      </c>
+      <c r="X15" s="25">
+        <v>83.411993337035</v>
+      </c>
+      <c r="Y15" s="25">
+        <v>84.418830717956</v>
+      </c>
+      <c r="Z15" s="25">
+        <v>85.055555555556</v>
+      </c>
+      <c r="AA15" s="25">
+        <v>82.948860478043</v>
+      </c>
+      <c r="AB15" s="25">
+        <v>85.85128561501</v>
+      </c>
+      <c r="AC15" s="25">
+        <v>87.380125086866</v>
+      </c>
+      <c r="AD15" s="25">
+        <v>87.446128180175</v>
+      </c>
+      <c r="AE15" s="25">
+        <v>87.77808676307</v>
+      </c>
+      <c r="AF15" s="38">
+        <v>86.588759042849</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32">
+      <c r="A16" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="C16" s="26">
+        <v>89.0</v>
+      </c>
+      <c r="D16" s="26">
+        <v>89.0</v>
+      </c>
+      <c r="E16" s="26">
+        <v>89.0</v>
+      </c>
+      <c r="F16" s="26">
+        <v>89.0</v>
+      </c>
+      <c r="G16" s="26">
+        <v>89.0</v>
+      </c>
+      <c r="H16" s="26">
+        <v>89.0</v>
+      </c>
+      <c r="I16" s="26">
+        <v>89.0</v>
+      </c>
+      <c r="J16" s="26">
+        <v>89.0</v>
+      </c>
+      <c r="K16" s="26">
+        <v>88.0</v>
+      </c>
+      <c r="L16" s="26">
+        <v>88.0</v>
+      </c>
+      <c r="M16" s="26">
+        <v>88.0</v>
+      </c>
+      <c r="N16" s="26">
+        <v>88.0</v>
+      </c>
+      <c r="O16" s="26">
+        <v>88.0</v>
+      </c>
+      <c r="P16" s="26">
+        <v>88.0</v>
+      </c>
+      <c r="Q16" s="26">
+        <v>88.0</v>
+      </c>
+      <c r="R16" s="26">
+        <v>88.0</v>
+      </c>
+      <c r="S16" s="26">
+        <v>88.0</v>
+      </c>
+      <c r="T16" s="26">
+        <v>88.0</v>
+      </c>
+      <c r="U16" s="26">
+        <v>88.0</v>
+      </c>
+      <c r="V16" s="26">
+        <v>88.0</v>
+      </c>
+      <c r="W16" s="26">
+        <v>88.0</v>
+      </c>
+      <c r="X16" s="26">
+        <v>88.0</v>
+      </c>
+      <c r="Y16" s="26">
+        <v>87.0</v>
+      </c>
+      <c r="Z16" s="26">
+        <v>87.0</v>
+      </c>
+      <c r="AA16" s="26">
+        <v>87.0</v>
+      </c>
+      <c r="AB16" s="26">
+        <v>87.0</v>
+      </c>
+      <c r="AC16" s="26">
+        <v>87.0</v>
+      </c>
+      <c r="AD16" s="26">
+        <v>87.0</v>
+      </c>
+      <c r="AE16" s="26">
+        <v>87.0</v>
+      </c>
+      <c r="AF16" s="39">
+        <v>87.0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:32">
+      <c r="A17" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="C17" s="21">
+        <v>906.625</v>
+      </c>
+      <c r="D17" s="21">
+        <v>906.0</v>
+      </c>
+      <c r="E17" s="21">
+        <v>905.875</v>
+      </c>
+      <c r="F17" s="21">
+        <v>905.375</v>
+      </c>
+      <c r="G17" s="21">
+        <v>651.51</v>
+      </c>
+      <c r="H17" s="21">
+        <v>904.5</v>
+      </c>
+      <c r="I17" s="21">
+        <v>904.125</v>
+      </c>
+      <c r="J17" s="21">
+        <v>903.5</v>
+      </c>
+      <c r="K17" s="21">
+        <v>902.75</v>
+      </c>
+      <c r="L17" s="21">
+        <v>902.375</v>
+      </c>
+      <c r="M17" s="21">
+        <v>901.875</v>
+      </c>
+      <c r="N17" s="21">
+        <v>649.17</v>
+      </c>
+      <c r="O17" s="21">
+        <v>901.25</v>
+      </c>
+      <c r="P17" s="21">
+        <v>901.25</v>
+      </c>
+      <c r="Q17" s="21">
+        <v>922.112</v>
+      </c>
+      <c r="R17" s="21">
+        <v>461.056</v>
+      </c>
+      <c r="S17" s="21">
+        <v>460.864</v>
+      </c>
+      <c r="T17" s="21">
+        <v>450.0</v>
+      </c>
+      <c r="U17" s="21">
+        <v>647.64</v>
+      </c>
+      <c r="V17" s="21">
+        <v>899.375</v>
+      </c>
+      <c r="W17" s="21">
+        <v>899.375</v>
+      </c>
+      <c r="X17" s="21">
+        <v>899.125</v>
+      </c>
+      <c r="Y17" s="21">
+        <v>899.0</v>
+      </c>
+      <c r="Z17" s="21">
+        <v>898.5</v>
+      </c>
+      <c r="AA17" s="21">
+        <v>898.125</v>
+      </c>
+      <c r="AB17" s="21">
+        <v>646.38</v>
+      </c>
+      <c r="AC17" s="21">
+        <v>897.25</v>
+      </c>
+      <c r="AD17" s="21">
+        <v>896.625</v>
+      </c>
+      <c r="AE17" s="21">
+        <v>896.125</v>
+      </c>
+      <c r="AF17" s="34">
+        <v>895.75</v>
+      </c>
+    </row>
+    <row r="18" spans="1:32">
+      <c r="A18" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="C18" s="19">
+        <v>7202.0</v>
+      </c>
+      <c r="D18" s="19">
+        <v>7202.0</v>
+      </c>
+      <c r="E18" s="19">
+        <v>7202.0</v>
+      </c>
+      <c r="F18" s="19">
+        <v>7202.0</v>
+      </c>
+      <c r="G18" s="19">
+        <v>7202.0</v>
+      </c>
+      <c r="H18" s="19">
+        <v>7202.0</v>
+      </c>
+      <c r="I18" s="19">
+        <v>7202.0</v>
+      </c>
+      <c r="J18" s="19">
+        <v>7202.0</v>
+      </c>
+      <c r="K18" s="19">
+        <v>7402.0</v>
+      </c>
+      <c r="L18" s="19">
+        <v>7402.0</v>
+      </c>
+      <c r="M18" s="19">
+        <v>7402.0</v>
+      </c>
+      <c r="N18" s="19">
+        <v>7402.0</v>
+      </c>
+      <c r="O18" s="19">
+        <v>7402.0</v>
+      </c>
+      <c r="P18" s="19">
+        <v>7402.0</v>
+      </c>
+      <c r="Q18" s="19">
+        <v>7402.0</v>
+      </c>
+      <c r="R18" s="19">
+        <v>7402.0</v>
+      </c>
+      <c r="S18" s="19">
+        <v>7402.0</v>
+      </c>
+      <c r="T18" s="19">
+        <v>7401.0</v>
+      </c>
+      <c r="U18" s="19">
+        <v>7401.0</v>
+      </c>
+      <c r="V18" s="19">
+        <v>7401.0</v>
+      </c>
+      <c r="W18" s="19">
+        <v>7401.0</v>
+      </c>
+      <c r="X18" s="19">
+        <v>7401.0</v>
+      </c>
+      <c r="Y18" s="19">
+        <v>7401.0</v>
+      </c>
+      <c r="Z18" s="19">
+        <v>7401.0</v>
+      </c>
+      <c r="AA18" s="19">
+        <v>7401.0</v>
+      </c>
+      <c r="AB18" s="19">
+        <v>7401.0</v>
+      </c>
+      <c r="AC18" s="19">
+        <v>7401.0</v>
+      </c>
+      <c r="AD18" s="19">
+        <v>7401.0</v>
+      </c>
+      <c r="AE18" s="19">
+        <v>7401.0</v>
+      </c>
+      <c r="AF18" s="32">
+        <v>7401.0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:32">
+      <c r="A19" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="C19" s="21"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="21"/>
+      <c r="I19" s="21"/>
+      <c r="J19" s="21"/>
+      <c r="K19" s="21"/>
+      <c r="L19" s="21"/>
+      <c r="M19" s="21"/>
+      <c r="N19" s="21"/>
+      <c r="O19" s="21"/>
+      <c r="P19" s="21"/>
+      <c r="Q19" s="21"/>
+      <c r="R19" s="21">
+        <v>461.056</v>
+      </c>
+      <c r="S19" s="21">
+        <v>460.864</v>
+      </c>
+      <c r="T19" s="21">
+        <v>450.0</v>
+      </c>
+      <c r="U19" s="21"/>
+      <c r="V19" s="21"/>
+      <c r="W19" s="21"/>
+      <c r="X19" s="21"/>
+      <c r="Y19" s="21"/>
+      <c r="Z19" s="21"/>
+      <c r="AA19" s="21"/>
+      <c r="AB19" s="21"/>
+      <c r="AC19" s="21"/>
+      <c r="AD19" s="21"/>
+      <c r="AE19" s="21"/>
+      <c r="AF19" s="34"/>
+    </row>
+    <row r="20" spans="1:32">
+      <c r="A20" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="19"/>
+      <c r="I20" s="19"/>
+      <c r="J20" s="19"/>
+      <c r="K20" s="19"/>
+      <c r="L20" s="19"/>
+      <c r="M20" s="19"/>
+      <c r="N20" s="19"/>
+      <c r="O20" s="19"/>
+      <c r="P20" s="19"/>
+      <c r="Q20" s="19"/>
+      <c r="R20" s="19">
+        <v>7532.0</v>
+      </c>
+      <c r="S20" s="19">
+        <v>7532.0</v>
+      </c>
+      <c r="T20" s="19">
+        <v>7532.0</v>
+      </c>
+      <c r="U20" s="19">
+        <v>7532.0</v>
+      </c>
+      <c r="V20" s="19">
+        <v>7532.0</v>
+      </c>
+      <c r="W20" s="19">
+        <v>7532.0</v>
+      </c>
+      <c r="X20" s="19">
+        <v>7531.0</v>
+      </c>
+      <c r="Y20" s="19">
+        <v>7531.0</v>
+      </c>
+      <c r="Z20" s="19">
+        <v>7531.0</v>
+      </c>
+      <c r="AA20" s="19">
+        <v>7531.0</v>
+      </c>
+      <c r="AB20" s="19">
+        <v>7531.0</v>
+      </c>
+      <c r="AC20" s="19">
+        <v>7531.0</v>
+      </c>
+      <c r="AD20" s="19">
+        <v>7531.0</v>
+      </c>
+      <c r="AE20" s="19">
+        <v>7531.0</v>
+      </c>
+      <c r="AF20" s="32">
+        <v>7531.0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:32">
+      <c r="A21" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="B21" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="C21" s="30">
+        <v>2.3038724341418</v>
+      </c>
+      <c r="D21" s="30">
+        <v>2.3400103311714</v>
+      </c>
+      <c r="E21" s="30">
+        <v>2.3119868986346</v>
+      </c>
+      <c r="F21" s="30">
+        <v>2.2928948294056</v>
+      </c>
+      <c r="G21" s="30">
+        <v>1.6670950316298</v>
+      </c>
+      <c r="H21" s="30">
+        <v>2.4039512151906</v>
+      </c>
+      <c r="I21" s="30">
+        <v>2.4036998744554</v>
+      </c>
+      <c r="J21" s="30">
+        <v>2.3886669408378</v>
+      </c>
+      <c r="K21" s="30">
+        <v>2.3610566235125</v>
+      </c>
+      <c r="L21" s="30">
+        <v>2.3614826553459</v>
+      </c>
+      <c r="M21" s="30">
+        <v>2.421863344771</v>
+      </c>
+      <c r="N21" s="30">
+        <v>1.7304022035304</v>
+      </c>
+      <c r="O21" s="30">
+        <v>2.489984804531</v>
+      </c>
+      <c r="P21" s="30">
+        <v>2.43223185103</v>
+      </c>
+      <c r="Q21" s="30">
+        <v>2.4100152458945</v>
+      </c>
+      <c r="R21" s="30">
+        <v>2.3819318915661</v>
+      </c>
+      <c r="S21" s="30">
+        <v>2.349681914743</v>
+      </c>
+      <c r="T21" s="30">
+        <v>2.3601054763188</v>
+      </c>
+      <c r="U21" s="30">
+        <v>1.6409104345256</v>
+      </c>
+      <c r="V21" s="30">
+        <v>2.2268800638266</v>
+      </c>
+      <c r="W21" s="30">
+        <v>2.2269719646738</v>
+      </c>
+      <c r="X21" s="30">
+        <v>2.2364748151731</v>
+      </c>
+      <c r="Y21" s="30">
+        <v>2.2879846166898</v>
+      </c>
+      <c r="Z21" s="30">
+        <v>2.3057183182926</v>
+      </c>
+      <c r="AA21" s="30">
+        <v>2.3430366537676</v>
+      </c>
+      <c r="AB21" s="30">
+        <v>1.7155217410537</v>
+      </c>
+      <c r="AC21" s="27">
+        <v>2.5032549056077</v>
+      </c>
+      <c r="AD21" s="30">
+        <v>2.4510600492057</v>
+      </c>
+      <c r="AE21" s="30">
+        <v>2.4334323989983</v>
+      </c>
+      <c r="AF21" s="44">
+        <v>2.4134085738235</v>
+      </c>
+    </row>
+    <row r="22" spans="1:32">
+      <c r="A22" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="28">
+        <v>2.9017921466103</v>
+      </c>
+      <c r="D22" s="28">
+        <v>2.947563085722</v>
+      </c>
+      <c r="E22" s="28">
+        <v>2.9290150949099</v>
+      </c>
+      <c r="F22" s="28">
+        <v>2.8449128445625</v>
+      </c>
+      <c r="G22" s="31">
+        <v>2.1819555833818</v>
+      </c>
+      <c r="H22" s="28">
+        <v>2.9831125762863</v>
+      </c>
+      <c r="I22" s="28">
+        <v>2.982975054366</v>
+      </c>
+      <c r="J22" s="28">
+        <v>2.9646084064034</v>
+      </c>
+      <c r="K22" s="28">
+        <v>2.9303505680015</v>
+      </c>
+      <c r="L22" s="28">
+        <v>2.9335336898586</v>
+      </c>
+      <c r="M22" s="28">
+        <v>3.0087779475948</v>
+      </c>
+      <c r="N22" s="31">
+        <v>2.1359512739498</v>
+      </c>
+      <c r="O22" s="28">
+        <v>3.0910960265734</v>
+      </c>
+      <c r="P22" s="28">
+        <v>3.053358015856</v>
+      </c>
+      <c r="Q22" s="28">
+        <v>3.014364880078</v>
+      </c>
+      <c r="R22" s="28">
+        <v>3.5695437944302</v>
+      </c>
+      <c r="S22" s="28">
+        <v>3.5216169712727</v>
+      </c>
+      <c r="T22" s="28">
+        <v>3.5606907079504</v>
+      </c>
+      <c r="U22" s="28">
+        <v>2.7203374426976</v>
+      </c>
+      <c r="V22" s="28">
+        <v>3.3266582598043</v>
+      </c>
+      <c r="W22" s="28">
+        <v>2.7791637945968</v>
+      </c>
+      <c r="X22" s="28">
+        <v>2.7911323232245</v>
+      </c>
+      <c r="Y22" s="28">
+        <v>2.8554728040829</v>
+      </c>
+      <c r="Z22" s="28">
+        <v>2.8778307836256</v>
+      </c>
+      <c r="AA22" s="28">
+        <v>2.9245810877719</v>
+      </c>
+      <c r="AB22" s="28">
+        <v>2.2806356012591</v>
+      </c>
+      <c r="AC22" s="28">
+        <v>3.1565517773356</v>
+      </c>
+      <c r="AD22" s="28">
+        <v>3.0910364109133</v>
+      </c>
+      <c r="AE22" s="28">
+        <v>3.0690457165938</v>
+      </c>
+      <c r="AF22" s="41">
+        <v>5.088764808729</v>
+      </c>
+    </row>
+    <row r="23" spans="1:32">
+      <c r="A23" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="B23" s="17"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="17"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="17"/>
+      <c r="I23" s="17"/>
+      <c r="J23" s="17"/>
+      <c r="K23" s="17"/>
+      <c r="L23" s="17"/>
+      <c r="M23" s="17"/>
+      <c r="N23" s="17"/>
+      <c r="O23" s="17"/>
+      <c r="P23" s="17"/>
+      <c r="Q23" s="17"/>
+      <c r="R23" s="17"/>
+      <c r="S23" s="17"/>
+      <c r="T23" s="17"/>
+      <c r="U23" s="17"/>
+      <c r="V23" s="17"/>
+      <c r="W23" s="17"/>
+      <c r="X23" s="17"/>
+      <c r="Y23" s="17"/>
+      <c r="Z23" s="17"/>
+      <c r="AA23" s="17"/>
+      <c r="AB23" s="17"/>
+      <c r="AC23" s="17"/>
+      <c r="AD23" s="17"/>
+      <c r="AE23" s="17"/>
+      <c r="AF23" s="42"/>
+    </row>
+    <row r="24" spans="1:32">
+      <c r="A24" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24" s="24">
+        <v>85.871964679912</v>
+      </c>
+      <c r="D24" s="24">
+        <v>84.752311301228</v>
+      </c>
+      <c r="E24" s="24">
+        <v>84.875051774127</v>
+      </c>
+      <c r="F24" s="24">
+        <v>84.993323203021</v>
+      </c>
+      <c r="G24" s="24">
+        <v>85.098811498065</v>
+      </c>
+      <c r="H24" s="24">
+        <v>84.60389879718</v>
+      </c>
+      <c r="I24" s="24">
+        <v>84.315624423538</v>
+      </c>
+      <c r="J24" s="24">
+        <v>84.206986588598</v>
+      </c>
+      <c r="K24" s="24">
+        <v>83.404903726278</v>
+      </c>
+      <c r="L24" s="24">
+        <v>83.236313236313</v>
+      </c>
+      <c r="M24" s="24">
+        <v>82.550025417071</v>
+      </c>
+      <c r="N24" s="24">
+        <v>82.000693481276</v>
+      </c>
+      <c r="O24" s="24">
+        <v>81.453536754508</v>
+      </c>
+      <c r="P24" s="24">
+        <v>81.450120303535</v>
+      </c>
+      <c r="Q24" s="24">
+        <v>81.730387879749</v>
+      </c>
+      <c r="R24" s="24">
+        <v>84.418830717956</v>
+      </c>
+      <c r="S24" s="24">
+        <v>84.743055555556</v>
+      </c>
+      <c r="T24" s="24">
+        <v>84.176394293126</v>
+      </c>
+      <c r="U24" s="24">
+        <v>84.603891591383</v>
+      </c>
+      <c r="V24" s="24">
+        <v>85.159138290479</v>
+      </c>
+      <c r="W24" s="24">
+        <v>85.560035219426</v>
+      </c>
+      <c r="X24" s="24">
+        <v>85.887096774194</v>
+      </c>
+      <c r="Y24" s="24">
+        <v>86.588759042849</v>
+      </c>
+      <c r="Z24" s="24">
+        <v>85.796798886569</v>
+      </c>
+      <c r="AA24" s="24">
+        <v>85.278009839413</v>
+      </c>
+      <c r="AB24" s="24">
+        <v>84.692811368069</v>
+      </c>
+      <c r="AC24" s="24">
+        <v>83.644221385752</v>
+      </c>
+      <c r="AD24" s="24">
+        <v>83.170595620031</v>
+      </c>
+      <c r="AE24" s="24">
+        <v>82.961205693553</v>
+      </c>
+      <c r="AF24" s="37">
+        <v>83.072625698324</v>
+      </c>
+    </row>
+    <row r="25" spans="1:32">
+      <c r="A25" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="B25" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="C25" s="30">
+        <v>2.3038724341418</v>
+      </c>
+      <c r="D25" s="30">
+        <v>2.3400103311714</v>
+      </c>
+      <c r="E25" s="30">
+        <v>2.3259151755468</v>
+      </c>
+      <c r="F25" s="30">
+        <v>2.3148078033451</v>
+      </c>
+      <c r="G25" s="30">
+        <v>2.1530285223282</v>
+      </c>
+      <c r="H25" s="30">
+        <v>2.201671031729</v>
+      </c>
+      <c r="I25" s="30">
+        <v>2.2344673555998</v>
+      </c>
+      <c r="J25" s="30">
+        <v>2.2561069268727</v>
+      </c>
+      <c r="K25" s="30">
+        <v>2.3610566235125</v>
+      </c>
+      <c r="L25" s="30">
+        <v>2.3612695759602</v>
+      </c>
+      <c r="M25" s="30">
+        <v>2.3811175996286</v>
+      </c>
+      <c r="N25" s="30">
+        <v>2.2196646862358</v>
+      </c>
+      <c r="O25" s="30">
+        <v>2.2718760561376</v>
+      </c>
+      <c r="P25" s="30">
+        <v>2.2983490589388</v>
+      </c>
+      <c r="Q25" s="30">
+        <v>2.3146121979433</v>
+      </c>
+      <c r="R25" s="30">
+        <v>2.3819318915661</v>
+      </c>
+      <c r="S25" s="30">
+        <v>2.3657003556842</v>
+      </c>
+      <c r="T25" s="30">
+        <v>2.3638622722965</v>
+      </c>
+      <c r="U25" s="30">
+        <v>2.1804162484776</v>
+      </c>
+      <c r="V25" s="30">
+        <v>2.1899938753637</v>
+      </c>
+      <c r="W25" s="30">
+        <v>2.196313309887</v>
+      </c>
+      <c r="X25" s="30">
+        <v>2.2021523587948</v>
+      </c>
+      <c r="Y25" s="30">
+        <v>2.2879846166898</v>
+      </c>
+      <c r="Z25" s="30">
+        <v>2.2968147711704</v>
+      </c>
+      <c r="AA25" s="30">
+        <v>2.3120109974936</v>
+      </c>
+      <c r="AB25" s="30">
+        <v>2.1663271957276</v>
+      </c>
+      <c r="AC25" s="30">
+        <v>2.2298502359697</v>
+      </c>
+      <c r="AD25" s="30">
+        <v>2.2655462184874</v>
+      </c>
+      <c r="AE25" s="30">
+        <v>2.2890073934776</v>
+      </c>
+      <c r="AF25" s="44">
+        <v>2.4134085738235</v>
+      </c>
+    </row>
+    <row r="26" spans="1:32">
+      <c r="A26" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="B26" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="C26" s="29">
+        <v>2.9017921466103</v>
+      </c>
+      <c r="D26" s="29">
+        <v>2.947563085722</v>
+      </c>
+      <c r="E26" s="29">
+        <v>2.9382338639474</v>
+      </c>
+      <c r="F26" s="29">
+        <v>2.9068425728896</v>
+      </c>
+      <c r="G26" s="29">
+        <v>2.7257874801044</v>
+      </c>
+      <c r="H26" s="29">
+        <v>2.7756711246138</v>
+      </c>
+      <c r="I26" s="29">
+        <v>2.8093237789976</v>
+      </c>
+      <c r="J26" s="29">
+        <v>2.8311156194695</v>
+      </c>
+      <c r="K26" s="29">
+        <v>2.9303505680015</v>
+      </c>
+      <c r="L26" s="29">
+        <v>2.9319416547176</v>
+      </c>
+      <c r="M26" s="29">
+        <v>2.957110060472</v>
+      </c>
+      <c r="N26" s="29">
+        <v>2.7533674116319</v>
+      </c>
+      <c r="O26" s="29">
+        <v>2.818598493034</v>
+      </c>
+      <c r="P26" s="29">
+        <v>2.8573547444651</v>
+      </c>
+      <c r="Q26" s="29">
+        <v>2.8802218068247</v>
+      </c>
+      <c r="R26" s="29">
+        <v>3.5695437944302</v>
+      </c>
+      <c r="S26" s="29">
+        <v>3.5454220422177</v>
+      </c>
+      <c r="T26" s="29">
+        <v>3.5504382506115</v>
+      </c>
+      <c r="U26" s="29">
+        <v>3.3398036209933</v>
+      </c>
+      <c r="V26" s="29">
+        <v>3.337093956197</v>
+      </c>
+      <c r="W26" s="29">
+        <v>3.2417455163347</v>
+      </c>
+      <c r="X26" s="29">
+        <v>3.1762312271085</v>
+      </c>
+      <c r="Y26" s="29">
+        <v>2.8554728040829</v>
+      </c>
+      <c r="Z26" s="29">
+        <v>2.8666055285224</v>
+      </c>
+      <c r="AA26" s="29">
+        <v>2.8856659750051</v>
+      </c>
+      <c r="AB26" s="29">
+        <v>2.7378961298995</v>
+      </c>
+      <c r="AC26" s="29">
+        <v>2.8168278376808</v>
+      </c>
+      <c r="AD26" s="29">
+        <v>2.8610760755556</v>
+      </c>
+      <c r="AE26" s="29">
+        <v>2.8901386948028</v>
+      </c>
+      <c r="AF26" s="43">
+        <v>5.088764808729</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells>
+    <mergeCell ref="A1:AF1"/>
+    <mergeCell ref="C6:C6"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="K6:Q6"/>
+    <mergeCell ref="R6:X6"/>
+    <mergeCell ref="Y6:AE6"/>
+    <mergeCell ref="AF6:AF6"/>
+    <mergeCell ref="A23:AF23"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12099,7 +13159,7 @@
         <v>2</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>181</v>
+        <v>212</v>
       </c>
     </row>
     <row r="3" spans="1:32">
@@ -12110,7 +13170,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="5">
-        <v>45775.0</v>
+        <v>45852.0</v>
       </c>
     </row>
     <row r="4" spans="1:32">
@@ -12132,10 +13192,10 @@
         <v>2</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>182</v>
+        <v>213</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>183</v>
+        <v>214</v>
       </c>
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
@@ -12144,7 +13204,7 @@
       <c r="I6" s="8"/>
       <c r="J6" s="8"/>
       <c r="K6" s="8" t="s">
-        <v>184</v>
+        <v>215</v>
       </c>
       <c r="L6" s="8"/>
       <c r="M6" s="8"/>
@@ -12153,7 +13213,7 @@
       <c r="P6" s="8"/>
       <c r="Q6" s="8"/>
       <c r="R6" s="8" t="s">
-        <v>185</v>
+        <v>216</v>
       </c>
       <c r="S6" s="8"/>
       <c r="T6" s="8"/>
@@ -12162,7 +13222,7 @@
       <c r="W6" s="8"/>
       <c r="X6" s="8"/>
       <c r="Y6" s="8" t="s">
-        <v>186</v>
+        <v>217</v>
       </c>
       <c r="Z6" s="8"/>
       <c r="AA6" s="8"/>
@@ -12171,101 +13231,101 @@
       <c r="AD6" s="8"/>
       <c r="AE6" s="8"/>
       <c r="AF6" s="11" t="s">
-        <v>187</v>
+        <v>218</v>
       </c>
     </row>
     <row r="7" spans="1:32" customHeight="1" ht="36">
       <c r="A7" s="7"/>
       <c r="B7" s="9"/>
       <c r="C7" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="I7" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="J7" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="K7" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="L7" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="G7" s="10" t="s">
+      <c r="M7" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="H7" s="10" t="s">
+      <c r="N7" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="I7" s="10" t="s">
+      <c r="O7" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="J7" s="10" t="s">
+      <c r="P7" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="K7" s="10" t="s">
+      <c r="Q7" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="L7" s="10" t="s">
+      <c r="R7" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="M7" s="10" t="s">
+      <c r="S7" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="N7" s="10" t="s">
+      <c r="T7" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="O7" s="10" t="s">
+      <c r="U7" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="P7" s="10" t="s">
+      <c r="V7" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="Q7" s="10" t="s">
+      <c r="W7" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="R7" s="10" t="s">
+      <c r="X7" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="S7" s="10" t="s">
+      <c r="Y7" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="T7" s="10" t="s">
+      <c r="Z7" s="10" t="s">
         <v>205</v>
       </c>
-      <c r="U7" s="10" t="s">
+      <c r="AA7" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="V7" s="10" t="s">
+      <c r="AB7" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="W7" s="10" t="s">
+      <c r="AC7" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="X7" s="10" t="s">
+      <c r="AD7" s="10" t="s">
         <v>209</v>
       </c>
-      <c r="Y7" s="10" t="s">
+      <c r="AE7" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="Z7" s="10" t="s">
+      <c r="AF7" s="12" t="s">
         <v>211</v>
-      </c>
-      <c r="AA7" s="10" t="s">
-        <v>212</v>
-      </c>
-      <c r="AB7" s="10" t="s">
-        <v>213</v>
-      </c>
-      <c r="AC7" s="10" t="s">
-        <v>214</v>
-      </c>
-      <c r="AD7" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="AE7" s="10" t="s">
-        <v>216</v>
-      </c>
-      <c r="AF7" s="12" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="8" spans="1:32">
@@ -12276,76 +13336,74 @@
         <v>2</v>
       </c>
       <c r="C8" s="19">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="D8" s="19">
         <v>1.0</v>
       </c>
       <c r="E8" s="19">
+        <v>4.0</v>
+      </c>
+      <c r="F8" s="19">
+        <v>3.0</v>
+      </c>
+      <c r="G8" s="19"/>
+      <c r="H8" s="19">
         <v>2.0</v>
       </c>
-      <c r="F8" s="19">
+      <c r="I8" s="19">
+        <v>2.0</v>
+      </c>
+      <c r="J8" s="19">
+        <v>2.0</v>
+      </c>
+      <c r="K8" s="19">
+        <v>2.0</v>
+      </c>
+      <c r="L8" s="19">
         <v>4.0</v>
       </c>
-      <c r="G8" s="19">
+      <c r="M8" s="19">
         <v>3.0</v>
-      </c>
-      <c r="H8" s="19">
-        <v>3.0</v>
-      </c>
-      <c r="I8" s="19">
-        <v>3.0</v>
-      </c>
-      <c r="J8" s="19">
-        <v>3.0</v>
-      </c>
-      <c r="K8" s="19">
-        <v>3.0</v>
-      </c>
-      <c r="L8" s="19">
-        <v>3.0</v>
-      </c>
-      <c r="M8" s="19">
-        <v>2.0</v>
       </c>
       <c r="N8" s="19">
         <v>3.0</v>
       </c>
-      <c r="O8" s="19"/>
+      <c r="O8" s="19">
+        <v>2.0</v>
+      </c>
       <c r="P8" s="19">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="Q8" s="19"/>
       <c r="R8" s="19">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="S8" s="19">
         <v>1.0</v>
       </c>
       <c r="T8" s="19">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="U8" s="19">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="V8" s="19"/>
       <c r="W8" s="19">
-        <v>2.0</v>
-      </c>
-      <c r="X8" s="19">
         <v>1.0</v>
       </c>
+      <c r="X8" s="19"/>
       <c r="Y8" s="19">
         <v>2.0</v>
       </c>
       <c r="Z8" s="19">
+        <v>1.0</v>
+      </c>
+      <c r="AA8" s="19">
         <v>3.0</v>
       </c>
-      <c r="AA8" s="19">
-        <v>2.0</v>
-      </c>
       <c r="AB8" s="19">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="AC8" s="19">
         <v>2.0</v>
@@ -12354,7 +13412,7 @@
         <v>3.0</v>
       </c>
       <c r="AE8" s="19">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="AF8" s="32">
         <v>3.0</v>
@@ -12406,94 +13464,94 @@
         <v>2</v>
       </c>
       <c r="C10" s="19">
-        <v>6224.0</v>
+        <v>6311.0</v>
       </c>
       <c r="D10" s="19">
-        <v>6142.0</v>
+        <v>6330.0</v>
       </c>
       <c r="E10" s="19">
-        <v>6153.0</v>
+        <v>6324.0</v>
       </c>
       <c r="F10" s="19">
+        <v>6329.0</v>
+      </c>
+      <c r="G10" s="19">
+        <v>6290.0</v>
+      </c>
+      <c r="H10" s="19">
         <v>6163.0</v>
       </c>
-      <c r="G10" s="19">
-        <v>6173.0</v>
-      </c>
-      <c r="H10" s="19">
-        <v>5966.0</v>
-      </c>
       <c r="I10" s="19">
-        <v>5969.0</v>
+        <v>6085.0</v>
       </c>
       <c r="J10" s="19">
-        <v>6004.0</v>
+        <v>6108.0</v>
       </c>
       <c r="K10" s="19">
-        <v>6021.0</v>
+        <v>6161.0</v>
       </c>
       <c r="L10" s="19">
-        <v>5990.0</v>
+        <v>6154.0</v>
       </c>
       <c r="M10" s="19">
-        <v>5852.0</v>
+        <v>6176.0</v>
       </c>
       <c r="N10" s="19">
-        <v>5786.0</v>
+        <v>6020.0</v>
       </c>
       <c r="O10" s="19">
-        <v>5715.0</v>
+        <v>5844.0</v>
       </c>
       <c r="P10" s="19">
-        <v>5842.0</v>
+        <v>5841.0</v>
       </c>
       <c r="Q10" s="19">
-        <v>6009.0</v>
+        <v>5954.0</v>
       </c>
       <c r="R10" s="19">
-        <v>6079.0</v>
+        <v>6077.0</v>
       </c>
       <c r="S10" s="19">
-        <v>6124.0</v>
+        <v>6158.0</v>
       </c>
       <c r="T10" s="19">
-        <v>5969.0</v>
+        <v>6170.0</v>
       </c>
       <c r="U10" s="19">
-        <v>6177.0</v>
+        <v>6236.0</v>
       </c>
       <c r="V10" s="19">
-        <v>6287.0</v>
+        <v>6416.0</v>
       </c>
       <c r="W10" s="19">
-        <v>6290.0</v>
+        <v>6515.0</v>
       </c>
       <c r="X10" s="19">
-        <v>6313.0</v>
+        <v>6474.0</v>
       </c>
       <c r="Y10" s="19">
-        <v>6224.0</v>
+        <v>6397.0</v>
       </c>
       <c r="Z10" s="19">
-        <v>6105.0</v>
+        <v>6459.0</v>
       </c>
       <c r="AA10" s="19">
-        <v>6045.0</v>
+        <v>6467.0</v>
       </c>
       <c r="AB10" s="19">
-        <v>5943.0</v>
+        <v>6260.0</v>
       </c>
       <c r="AC10" s="19">
-        <v>5682.0</v>
+        <v>6053.0</v>
       </c>
       <c r="AD10" s="19">
-        <v>5776.0</v>
+        <v>6120.0</v>
       </c>
       <c r="AE10" s="19">
-        <v>5840.0</v>
+        <v>6273.0</v>
       </c>
       <c r="AF10" s="32">
-        <v>5948.0</v>
+        <v>6276.0</v>
       </c>
     </row>
     <row r="11" spans="1:32">
@@ -12504,94 +13562,94 @@
         <v>2</v>
       </c>
       <c r="C11" s="21">
-        <v>393.52222222222</v>
+        <v>396.53888888889</v>
       </c>
       <c r="D11" s="21">
-        <v>387.17777777778</v>
+        <v>392.93333333333</v>
       </c>
       <c r="E11" s="21">
-        <v>391.81666666667</v>
+        <v>386.76666666667</v>
       </c>
       <c r="F11" s="21">
-        <v>394.86111111111</v>
+        <v>400.13888888889</v>
       </c>
       <c r="G11" s="21">
-        <v>390.80555555556</v>
+        <v>395.35555555556</v>
       </c>
       <c r="H11" s="21">
-        <v>376.25555555556</v>
+        <v>387.06111111111</v>
       </c>
       <c r="I11" s="21">
-        <v>376.13888888889</v>
+        <v>384.59444444444</v>
       </c>
       <c r="J11" s="21">
-        <v>378.24444444444</v>
+        <v>382.36666666667</v>
       </c>
       <c r="K11" s="21">
-        <v>382.35</v>
+        <v>389.17222222222</v>
       </c>
       <c r="L11" s="21">
-        <v>382.12222222222</v>
+        <v>389.31111111111</v>
       </c>
       <c r="M11" s="21">
-        <v>372.38888888889</v>
+        <v>394.88888888889</v>
       </c>
       <c r="N11" s="21">
-        <v>375.15555555556</v>
+        <v>385.15555555556</v>
       </c>
       <c r="O11" s="21">
-        <v>361.95</v>
+        <v>364.43333333333</v>
       </c>
       <c r="P11" s="21">
-        <v>370.54444444444</v>
+        <v>370.35</v>
       </c>
       <c r="Q11" s="21">
-        <v>382.61666666667</v>
+        <v>375.22222222222</v>
       </c>
       <c r="R11" s="21">
-        <v>387.12777777778</v>
+        <v>390.73888888889</v>
       </c>
       <c r="S11" s="21">
-        <v>392.27777777778</v>
+        <v>389.28888888889</v>
       </c>
       <c r="T11" s="21">
-        <v>381.33888888889</v>
+        <v>391.82222222222</v>
       </c>
       <c r="U11" s="21">
-        <v>394.68333333333</v>
+        <v>397.85555555556</v>
       </c>
       <c r="V11" s="21">
-        <v>403.87222222222</v>
+        <v>410.15555555556</v>
       </c>
       <c r="W11" s="21">
-        <v>403.85555555556</v>
+        <v>404.20555555556</v>
       </c>
       <c r="X11" s="21">
-        <v>402.02777777778</v>
+        <v>406.53333333333</v>
       </c>
       <c r="Y11" s="21">
-        <v>392.92222222222</v>
+        <v>407.26111111111</v>
       </c>
       <c r="Z11" s="21">
-        <v>389.68333333333</v>
+        <v>417.31666666667</v>
       </c>
       <c r="AA11" s="21">
-        <v>383.31666666667</v>
+        <v>411.27222222222</v>
       </c>
       <c r="AB11" s="21">
-        <v>376.78333333333</v>
+        <v>397.52222222222</v>
       </c>
       <c r="AC11" s="21">
-        <v>358.43333333333</v>
+        <v>382.47222222222</v>
       </c>
       <c r="AD11" s="21">
-        <v>365.81111111111</v>
+        <v>387.7</v>
       </c>
       <c r="AE11" s="21">
-        <v>368.25555555556</v>
+        <v>389.75</v>
       </c>
       <c r="AF11" s="34">
-        <v>371.15555555556</v>
+        <v>393.93333333333</v>
       </c>
     </row>
     <row r="12" spans="1:32">
@@ -12602,94 +13660,94 @@
         <v>2</v>
       </c>
       <c r="C12" s="22">
-        <v>63.226578120537</v>
+        <v>62.832972411486</v>
       </c>
       <c r="D12" s="22">
-        <v>63.037736531712</v>
+        <v>62.074776197999</v>
       </c>
       <c r="E12" s="22">
-        <v>63.67896419091</v>
+        <v>61.158549441282</v>
       </c>
       <c r="F12" s="22">
-        <v>64.069626985415</v>
+        <v>63.223082459929</v>
       </c>
       <c r="G12" s="22">
-        <v>63.308853969797</v>
+        <v>62.854619325208</v>
       </c>
       <c r="H12" s="22">
-        <v>63.066636868179</v>
+        <v>62.804009591289</v>
       </c>
       <c r="I12" s="22">
-        <v>63.015394352302</v>
+        <v>63.203688487172</v>
       </c>
       <c r="J12" s="22">
-        <v>62.998741579688</v>
+        <v>62.600960488976</v>
       </c>
       <c r="K12" s="22">
-        <v>63.50274040857</v>
+        <v>63.167054410359</v>
       </c>
       <c r="L12" s="22">
-        <v>63.793359302541</v>
+        <v>63.261474018705</v>
       </c>
       <c r="M12" s="22">
-        <v>63.634464950254</v>
+        <v>63.939263097294</v>
       </c>
       <c r="N12" s="22">
-        <v>64.838499059031</v>
+        <v>63.979328165375</v>
       </c>
       <c r="O12" s="22">
-        <v>63.333333333333</v>
+        <v>62.36025553274</v>
       </c>
       <c r="P12" s="22">
-        <v>63.427669367416</v>
+        <v>63.405238828968</v>
       </c>
       <c r="Q12" s="22">
-        <v>63.673933544128</v>
+        <v>63.020191841153</v>
       </c>
       <c r="R12" s="22">
-        <v>63.682806017072</v>
+        <v>64.297990602088</v>
       </c>
       <c r="S12" s="22">
-        <v>64.05580956528</v>
+        <v>63.216773122587</v>
       </c>
       <c r="T12" s="22">
-        <v>63.886562052084</v>
+        <v>63.504412029534</v>
       </c>
       <c r="U12" s="22">
-        <v>63.895634342453</v>
+        <v>63.799800441879</v>
       </c>
       <c r="V12" s="22">
-        <v>64.239259141438</v>
+        <v>63.926988085342</v>
       </c>
       <c r="W12" s="22">
-        <v>64.205970676559</v>
+        <v>62.042295557261</v>
       </c>
       <c r="X12" s="22">
-        <v>63.682524596512</v>
+        <v>62.794768818865</v>
       </c>
       <c r="Y12" s="22">
-        <v>63.130177092259</v>
+        <v>63.66439129453</v>
       </c>
       <c r="Z12" s="22">
-        <v>63.830193830194</v>
+        <v>64.610104763379</v>
       </c>
       <c r="AA12" s="22">
-        <v>63.41053212021</v>
+        <v>63.595519131316</v>
       </c>
       <c r="AB12" s="22">
-        <v>63.3995176398</v>
+        <v>63.501952431665</v>
       </c>
       <c r="AC12" s="22">
-        <v>63.08224803473</v>
+        <v>63.187216623529</v>
       </c>
       <c r="AD12" s="22">
-        <v>63.332948599569</v>
+        <v>63.349673202614</v>
       </c>
       <c r="AE12" s="22">
-        <v>63.057458143075</v>
+        <v>62.131356607684</v>
       </c>
       <c r="AF12" s="35">
-        <v>62.400059777329</v>
+        <v>62.768217548332</v>
       </c>
     </row>
     <row r="13" spans="1:32">
@@ -12700,94 +13758,94 @@
         <v>2</v>
       </c>
       <c r="C13" s="23">
-        <v>63.8</v>
+        <v>63.6</v>
       </c>
       <c r="D13" s="23">
-        <v>63.9</v>
+        <v>63.6</v>
       </c>
       <c r="E13" s="23">
-        <v>63.9</v>
+        <v>63.6</v>
       </c>
       <c r="F13" s="23">
-        <v>63.9</v>
+        <v>63.6</v>
       </c>
       <c r="G13" s="23">
-        <v>63.9</v>
+        <v>63.6</v>
       </c>
       <c r="H13" s="23">
-        <v>63.9</v>
+        <v>63.6</v>
       </c>
       <c r="I13" s="23">
-        <v>63.9</v>
+        <v>63.6</v>
       </c>
       <c r="J13" s="23">
-        <v>63.9</v>
+        <v>63.6</v>
       </c>
       <c r="K13" s="23">
-        <v>63.9</v>
+        <v>63.6</v>
       </c>
       <c r="L13" s="23">
-        <v>63.9</v>
+        <v>63.6</v>
       </c>
       <c r="M13" s="23">
-        <v>63.9</v>
+        <v>63.6</v>
       </c>
       <c r="N13" s="23">
-        <v>63.9</v>
+        <v>63.6</v>
       </c>
       <c r="O13" s="23">
-        <v>63.9</v>
+        <v>63.6</v>
       </c>
       <c r="P13" s="23">
-        <v>63.9</v>
+        <v>63.6</v>
       </c>
       <c r="Q13" s="23">
-        <v>63.9</v>
+        <v>63.6</v>
       </c>
       <c r="R13" s="23">
-        <v>63.9</v>
+        <v>63.6</v>
       </c>
       <c r="S13" s="23">
-        <v>63.9</v>
+        <v>63.6</v>
       </c>
       <c r="T13" s="23">
-        <v>63.9</v>
+        <v>63.6</v>
       </c>
       <c r="U13" s="23">
-        <v>63.9</v>
+        <v>63.6</v>
       </c>
       <c r="V13" s="23">
-        <v>63.9</v>
+        <v>63.6</v>
       </c>
       <c r="W13" s="23">
-        <v>63.9</v>
+        <v>63.6</v>
       </c>
       <c r="X13" s="23">
-        <v>63.9</v>
+        <v>63.6</v>
       </c>
       <c r="Y13" s="23">
-        <v>63.9</v>
+        <v>63.7</v>
       </c>
       <c r="Z13" s="23">
-        <v>63.9</v>
+        <v>63.7</v>
       </c>
       <c r="AA13" s="23">
-        <v>63.9</v>
+        <v>63.7</v>
       </c>
       <c r="AB13" s="23">
-        <v>63.9</v>
+        <v>63.7</v>
       </c>
       <c r="AC13" s="23">
-        <v>63.9</v>
+        <v>63.7</v>
       </c>
       <c r="AD13" s="23">
-        <v>63.9</v>
+        <v>63.7</v>
       </c>
       <c r="AE13" s="23">
-        <v>63.9</v>
+        <v>63.7</v>
       </c>
       <c r="AF13" s="36">
-        <v>64.0</v>
+        <v>63.7</v>
       </c>
     </row>
     <row r="14" spans="1:32">
@@ -12798,94 +13856,94 @@
         <v>2</v>
       </c>
       <c r="C14" s="24">
-        <v>85.871964679912</v>
+        <v>84.450689147598</v>
       </c>
       <c r="D14" s="24">
-        <v>84.752311301228</v>
+        <v>84.716274089936</v>
       </c>
       <c r="E14" s="24">
-        <v>84.950987160017</v>
+        <v>84.715338245144</v>
       </c>
       <c r="F14" s="24">
-        <v>85.136068517751</v>
+        <v>84.816403109086</v>
       </c>
       <c r="G14" s="24">
-        <v>85.309563294638</v>
+        <v>84.305052941965</v>
       </c>
       <c r="H14" s="24">
-        <v>82.483063735656</v>
+        <v>82.625016758279</v>
       </c>
       <c r="I14" s="24">
-        <v>82.581627006087</v>
+        <v>81.623071763917</v>
       </c>
       <c r="J14" s="24">
-        <v>83.134865688175</v>
+        <v>81.953575741312</v>
       </c>
       <c r="K14" s="24">
-        <v>83.404903726278</v>
+        <v>82.686887666085</v>
       </c>
       <c r="L14" s="24">
-        <v>83.021483021483</v>
+        <v>82.637303612193</v>
       </c>
       <c r="M14" s="24">
-        <v>81.13129072508</v>
+        <v>82.966147232671</v>
       </c>
       <c r="N14" s="24">
-        <v>80.249653259362</v>
+        <v>80.903104421449</v>
       </c>
       <c r="O14" s="24">
-        <v>79.264909847434</v>
+        <v>78.558946094905</v>
       </c>
       <c r="P14" s="24">
-        <v>81.093836757357</v>
+        <v>78.560860793544</v>
       </c>
       <c r="Q14" s="24">
-        <v>83.411993337035</v>
+        <v>80.080699394755</v>
       </c>
       <c r="R14" s="24">
-        <v>84.418830717956</v>
+        <v>81.757029463205</v>
       </c>
       <c r="S14" s="24">
-        <v>85.055555555556</v>
+        <v>82.857911733046</v>
       </c>
       <c r="T14" s="24">
-        <v>82.948860478043</v>
+        <v>83.041722745626</v>
       </c>
       <c r="U14" s="24">
-        <v>85.85128561501</v>
+        <v>83.952611739365</v>
       </c>
       <c r="V14" s="24">
-        <v>87.380125086866</v>
+        <v>86.39913816321</v>
       </c>
       <c r="W14" s="24">
-        <v>87.446128180175</v>
+        <v>87.744107744108</v>
       </c>
       <c r="X14" s="24">
-        <v>87.77808676307</v>
+        <v>87.191919191919</v>
       </c>
       <c r="Y14" s="24">
-        <v>86.588759042849</v>
+        <v>86.178095109794</v>
       </c>
       <c r="Z14" s="24">
-        <v>84.968684759916</v>
+        <v>87.025060630558</v>
       </c>
       <c r="AA14" s="24">
-        <v>84.168755221387</v>
+        <v>87.168081951746</v>
       </c>
       <c r="AB14" s="24">
-        <v>82.794650320424</v>
+        <v>84.400701092086</v>
       </c>
       <c r="AC14" s="24">
-        <v>79.213718109578</v>
+        <v>81.631827376939</v>
       </c>
       <c r="AD14" s="24">
-        <v>80.569117031664</v>
+        <v>82.56880733945</v>
       </c>
       <c r="AE14" s="24">
-        <v>81.495953111917</v>
+        <v>84.655870445344</v>
       </c>
       <c r="AF14" s="37">
-        <v>83.072625698324</v>
+        <v>84.73066018631</v>
       </c>
     </row>
     <row r="15" spans="1:32">
@@ -12896,94 +13954,94 @@
         <v>2</v>
       </c>
       <c r="C15" s="25">
-        <v>85.267795676718</v>
+        <v>84.750968086527</v>
       </c>
       <c r="D15" s="25">
-        <v>84.974521415783</v>
+        <v>84.448897795591</v>
       </c>
       <c r="E15" s="25">
-        <v>85.289256198347</v>
+        <v>86.531266702298</v>
       </c>
       <c r="F15" s="25">
-        <v>85.163245626119</v>
+        <v>86.500935578722</v>
       </c>
       <c r="G15" s="25">
-        <v>85.804851157663</v>
+        <v>84.810803583367</v>
       </c>
       <c r="H15" s="25">
-        <v>85.732009925558</v>
+        <v>83.828250401284</v>
       </c>
       <c r="I15" s="25">
-        <v>85.219909003171</v>
+        <v>84.037998394434</v>
       </c>
       <c r="J15" s="25">
-        <v>85.871964679912</v>
+        <v>84.450689147598</v>
       </c>
       <c r="K15" s="25">
-        <v>84.752311301228</v>
+        <v>84.716274089936</v>
       </c>
       <c r="L15" s="25">
-        <v>84.950987160017</v>
+        <v>84.715338245144</v>
       </c>
       <c r="M15" s="25">
-        <v>85.136068517751</v>
+        <v>84.816403109086</v>
       </c>
       <c r="N15" s="25">
-        <v>85.309563294638</v>
+        <v>84.305052941965</v>
       </c>
       <c r="O15" s="25">
-        <v>82.483063735656</v>
+        <v>82.625016758279</v>
       </c>
       <c r="P15" s="25">
-        <v>82.581627006087</v>
+        <v>81.623071763917</v>
       </c>
       <c r="Q15" s="25">
-        <v>83.134865688175</v>
+        <v>81.953575741312</v>
       </c>
       <c r="R15" s="25">
-        <v>83.404903726278</v>
+        <v>82.686887666085</v>
       </c>
       <c r="S15" s="25">
-        <v>83.021483021483</v>
+        <v>82.637303612193</v>
       </c>
       <c r="T15" s="25">
-        <v>81.13129072508</v>
+        <v>82.966147232671</v>
       </c>
       <c r="U15" s="25">
-        <v>80.249653259362</v>
+        <v>80.903104421449</v>
       </c>
       <c r="V15" s="25">
-        <v>79.264909847434</v>
+        <v>78.558946094905</v>
       </c>
       <c r="W15" s="25">
-        <v>81.093836757357</v>
+        <v>78.560860793544</v>
       </c>
       <c r="X15" s="25">
-        <v>83.411993337035</v>
+        <v>80.080699394755</v>
       </c>
       <c r="Y15" s="25">
-        <v>84.418830717956</v>
+        <v>81.757029463205</v>
       </c>
       <c r="Z15" s="25">
-        <v>85.055555555556</v>
+        <v>82.857911733046</v>
       </c>
       <c r="AA15" s="25">
-        <v>82.948860478043</v>
+        <v>83.041722745626</v>
       </c>
       <c r="AB15" s="25">
-        <v>85.85128561501</v>
+        <v>83.952611739365</v>
       </c>
       <c r="AC15" s="25">
-        <v>87.380125086866</v>
+        <v>86.39913816321</v>
       </c>
       <c r="AD15" s="25">
-        <v>87.446128180175</v>
+        <v>87.744107744108</v>
       </c>
       <c r="AE15" s="25">
-        <v>87.77808676307</v>
+        <v>87.191919191919</v>
       </c>
       <c r="AF15" s="38">
-        <v>86.588759042849</v>
+        <v>86.178095109794</v>
       </c>
     </row>
     <row r="16" spans="1:32">
@@ -12994,94 +14052,94 @@
         <v>2</v>
       </c>
       <c r="C16" s="26">
-        <v>89.0</v>
+        <v>93.0</v>
       </c>
       <c r="D16" s="26">
-        <v>89.0</v>
+        <v>92.0</v>
       </c>
       <c r="E16" s="26">
-        <v>89.0</v>
+        <v>92.0</v>
       </c>
       <c r="F16" s="26">
-        <v>89.0</v>
+        <v>92.0</v>
       </c>
       <c r="G16" s="26">
-        <v>89.0</v>
+        <v>92.0</v>
       </c>
       <c r="H16" s="26">
-        <v>89.0</v>
+        <v>92.0</v>
       </c>
       <c r="I16" s="26">
-        <v>89.0</v>
+        <v>92.0</v>
       </c>
       <c r="J16" s="26">
-        <v>89.0</v>
+        <v>92.0</v>
       </c>
       <c r="K16" s="26">
-        <v>88.0</v>
+        <v>92.0</v>
       </c>
       <c r="L16" s="26">
-        <v>88.0</v>
+        <v>92.0</v>
       </c>
       <c r="M16" s="26">
-        <v>88.0</v>
+        <v>92.0</v>
       </c>
       <c r="N16" s="26">
-        <v>88.0</v>
+        <v>92.0</v>
       </c>
       <c r="O16" s="26">
-        <v>88.0</v>
+        <v>92.0</v>
       </c>
       <c r="P16" s="26">
-        <v>88.0</v>
+        <v>92.0</v>
       </c>
       <c r="Q16" s="26">
-        <v>88.0</v>
+        <v>92.0</v>
       </c>
       <c r="R16" s="26">
-        <v>88.0</v>
+        <v>92.0</v>
       </c>
       <c r="S16" s="26">
-        <v>88.0</v>
+        <v>92.0</v>
       </c>
       <c r="T16" s="26">
-        <v>88.0</v>
+        <v>92.0</v>
       </c>
       <c r="U16" s="26">
-        <v>88.0</v>
+        <v>92.0</v>
       </c>
       <c r="V16" s="26">
-        <v>88.0</v>
+        <v>92.0</v>
       </c>
       <c r="W16" s="26">
-        <v>88.0</v>
+        <v>92.0</v>
       </c>
       <c r="X16" s="26">
-        <v>88.0</v>
+        <v>92.0</v>
       </c>
       <c r="Y16" s="26">
-        <v>87.0</v>
+        <v>92.0</v>
       </c>
       <c r="Z16" s="26">
-        <v>87.0</v>
+        <v>92.0</v>
       </c>
       <c r="AA16" s="26">
-        <v>87.0</v>
+        <v>92.0</v>
       </c>
       <c r="AB16" s="26">
-        <v>87.0</v>
+        <v>92.0</v>
       </c>
       <c r="AC16" s="26">
-        <v>87.0</v>
+        <v>92.0</v>
       </c>
       <c r="AD16" s="26">
-        <v>87.0</v>
+        <v>92.0</v>
       </c>
       <c r="AE16" s="26">
-        <v>87.0</v>
+        <v>92.0</v>
       </c>
       <c r="AF16" s="39">
-        <v>87.0</v>
+        <v>91.0</v>
       </c>
     </row>
     <row r="17" spans="1:32">
@@ -13092,94 +14150,94 @@
         <v>2</v>
       </c>
       <c r="C17" s="21">
-        <v>906.625</v>
+        <v>934.25</v>
       </c>
       <c r="D17" s="21">
-        <v>906.0</v>
+        <v>934.125</v>
       </c>
       <c r="E17" s="21">
-        <v>905.875</v>
+        <v>934.0</v>
       </c>
       <c r="F17" s="21">
-        <v>905.375</v>
+        <v>933.125</v>
       </c>
       <c r="G17" s="21">
-        <v>651.51</v>
+        <v>671.58</v>
       </c>
       <c r="H17" s="21">
-        <v>904.5</v>
+        <v>932.625</v>
       </c>
       <c r="I17" s="21">
-        <v>904.125</v>
+        <v>932.375</v>
       </c>
       <c r="J17" s="21">
-        <v>903.5</v>
+        <v>931.875</v>
       </c>
       <c r="K17" s="21">
-        <v>902.75</v>
+        <v>931.625</v>
       </c>
       <c r="L17" s="21">
-        <v>902.375</v>
+        <v>931.375</v>
       </c>
       <c r="M17" s="21">
-        <v>901.875</v>
+        <v>930.875</v>
       </c>
       <c r="N17" s="21">
-        <v>649.17</v>
+        <v>669.96</v>
       </c>
       <c r="O17" s="21">
-        <v>901.25</v>
+        <v>930.125</v>
       </c>
       <c r="P17" s="21">
-        <v>901.25</v>
+        <v>930.125</v>
       </c>
       <c r="Q17" s="21">
-        <v>922.112</v>
+        <v>951.936</v>
       </c>
       <c r="R17" s="21">
-        <v>461.056</v>
+        <v>475.84</v>
       </c>
       <c r="S17" s="21">
-        <v>460.864</v>
+        <v>475.712</v>
       </c>
       <c r="T17" s="21">
-        <v>450.0</v>
+        <v>464.5</v>
       </c>
       <c r="U17" s="21">
-        <v>647.64</v>
+        <v>668.7</v>
       </c>
       <c r="V17" s="21">
-        <v>899.375</v>
+        <v>928.5</v>
       </c>
       <c r="W17" s="21">
-        <v>899.375</v>
+        <v>928.25</v>
       </c>
       <c r="X17" s="21">
-        <v>899.125</v>
+        <v>928.125</v>
       </c>
       <c r="Y17" s="21">
-        <v>899.0</v>
+        <v>928.125</v>
       </c>
       <c r="Z17" s="21">
-        <v>898.5</v>
+        <v>927.875</v>
       </c>
       <c r="AA17" s="21">
-        <v>898.125</v>
+        <v>927.75</v>
       </c>
       <c r="AB17" s="21">
-        <v>646.38</v>
+        <v>667.71</v>
       </c>
       <c r="AC17" s="21">
-        <v>897.25</v>
+        <v>927.125</v>
       </c>
       <c r="AD17" s="21">
-        <v>896.625</v>
+        <v>926.875</v>
       </c>
       <c r="AE17" s="21">
-        <v>896.125</v>
+        <v>926.5</v>
       </c>
       <c r="AF17" s="34">
-        <v>895.75</v>
+        <v>926.25</v>
       </c>
     </row>
     <row r="18" spans="1:32">
@@ -13303,13 +14361,13 @@
       <c r="P19" s="21"/>
       <c r="Q19" s="21"/>
       <c r="R19" s="21">
-        <v>461.056</v>
+        <v>475.84</v>
       </c>
       <c r="S19" s="21">
-        <v>460.864</v>
+        <v>475.712</v>
       </c>
       <c r="T19" s="21">
-        <v>450.0</v>
+        <v>464.5</v>
       </c>
       <c r="U19" s="21"/>
       <c r="V19" s="21"/>
@@ -13400,94 +14458,94 @@
         <v>2</v>
       </c>
       <c r="C21" s="30">
-        <v>2.3038724341418</v>
+        <v>2.3560110399709</v>
       </c>
       <c r="D21" s="30">
-        <v>2.3400103311714</v>
+        <v>2.3773116728877</v>
       </c>
       <c r="E21" s="30">
-        <v>2.3119868986346</v>
+        <v>2.4148927001638</v>
       </c>
       <c r="F21" s="30">
-        <v>2.2928948294056</v>
+        <v>2.3320027768136</v>
       </c>
       <c r="G21" s="30">
-        <v>1.6670950316298</v>
+        <v>1.6986734865943</v>
       </c>
       <c r="H21" s="30">
-        <v>2.4039512151906</v>
+        <v>2.4095032366408</v>
       </c>
       <c r="I21" s="30">
-        <v>2.4036998744554</v>
+        <v>2.4243069900472</v>
       </c>
       <c r="J21" s="30">
-        <v>2.3886669408378</v>
+        <v>2.4371240519571</v>
       </c>
       <c r="K21" s="30">
-        <v>2.3610566235125</v>
+        <v>2.3938630426404</v>
       </c>
       <c r="L21" s="30">
-        <v>2.3614826553459</v>
+        <v>2.392366858839</v>
       </c>
       <c r="M21" s="30">
-        <v>2.421863344771</v>
+        <v>2.3573086662915</v>
       </c>
       <c r="N21" s="30">
-        <v>1.7304022035304</v>
-      </c>
-      <c r="O21" s="30">
-        <v>2.489984804531</v>
-      </c>
-      <c r="P21" s="30">
-        <v>2.43223185103</v>
-      </c>
-      <c r="Q21" s="30">
-        <v>2.4100152458945</v>
+        <v>1.7394530348488</v>
+      </c>
+      <c r="O21" s="27">
+        <v>2.5522500685997</v>
+      </c>
+      <c r="P21" s="27">
+        <v>2.5114756311597</v>
+      </c>
+      <c r="Q21" s="27">
+        <v>2.5369925969796</v>
       </c>
       <c r="R21" s="30">
-        <v>2.3819318915661</v>
+        <v>2.4355906900033</v>
       </c>
       <c r="S21" s="30">
-        <v>2.349681914743</v>
+        <v>2.4440050234045</v>
       </c>
       <c r="T21" s="30">
-        <v>2.3601054763188</v>
+        <v>2.37097323049</v>
       </c>
       <c r="U21" s="30">
-        <v>1.6409104345256</v>
+        <v>1.6807607451057</v>
       </c>
       <c r="V21" s="30">
-        <v>2.2268800638266</v>
+        <v>2.2637752614184</v>
       </c>
       <c r="W21" s="30">
-        <v>2.2269719646738</v>
+        <v>2.2964800637739</v>
       </c>
       <c r="X21" s="30">
-        <v>2.2364748151731</v>
+        <v>2.2830231223352</v>
       </c>
       <c r="Y21" s="30">
-        <v>2.2879846166898</v>
+        <v>2.2789433478385</v>
       </c>
       <c r="Z21" s="30">
-        <v>2.3057183182926</v>
+        <v>2.2234314469428</v>
       </c>
       <c r="AA21" s="30">
-        <v>2.3430366537676</v>
+        <v>2.2558051574383</v>
       </c>
       <c r="AB21" s="30">
-        <v>1.7155217410537</v>
-      </c>
-      <c r="AC21" s="27">
-        <v>2.5032549056077</v>
+        <v>1.6796796824776</v>
+      </c>
+      <c r="AC21" s="30">
+        <v>2.4240322463505</v>
       </c>
       <c r="AD21" s="30">
-        <v>2.4510600492057</v>
+        <v>2.3907015733815</v>
       </c>
       <c r="AE21" s="30">
-        <v>2.4334323989983</v>
+        <v>2.3771648492623</v>
       </c>
       <c r="AF21" s="44">
-        <v>2.4134085738235</v>
+        <v>2.3512861736334</v>
       </c>
     </row>
     <row r="22" spans="1:32">
@@ -13498,94 +14556,94 @@
         <v>2</v>
       </c>
       <c r="C22" s="28">
-        <v>2.9017921466103</v>
+        <v>2.9553322070354</v>
       </c>
       <c r="D22" s="28">
-        <v>2.947563085722</v>
+        <v>2.9820510656337</v>
       </c>
       <c r="E22" s="28">
-        <v>2.9290150949099</v>
+        <v>3.0466854376556</v>
       </c>
       <c r="F22" s="28">
-        <v>2.8449128445625</v>
-      </c>
-      <c r="G22" s="31">
-        <v>2.1819555833818</v>
+        <v>2.8813182735974</v>
+      </c>
+      <c r="G22" s="28">
+        <v>2.2109601531893</v>
       </c>
       <c r="H22" s="28">
-        <v>2.9831125762863</v>
+        <v>2.9772933768118</v>
       </c>
       <c r="I22" s="28">
-        <v>2.982975054366</v>
+        <v>2.995695838723</v>
       </c>
       <c r="J22" s="28">
-        <v>2.9646084064034</v>
+        <v>3.0117556450655</v>
       </c>
       <c r="K22" s="28">
-        <v>2.9303505680015</v>
+        <v>2.9580646222874</v>
       </c>
       <c r="L22" s="28">
-        <v>2.9335336898586</v>
+        <v>2.9587614002572</v>
       </c>
       <c r="M22" s="28">
-        <v>3.0087779475948</v>
-      </c>
-      <c r="N22" s="31">
-        <v>2.1359512739498</v>
+        <v>2.9156195196378</v>
+      </c>
+      <c r="N22" s="28">
+        <v>2.7902165535899</v>
       </c>
       <c r="O22" s="28">
-        <v>3.0910960265734</v>
+        <v>3.1544844838278</v>
       </c>
       <c r="P22" s="28">
-        <v>3.053358015856</v>
+        <v>3.1372607601796</v>
       </c>
       <c r="Q22" s="28">
-        <v>3.014364880078</v>
+        <v>3.1584624776661</v>
       </c>
       <c r="R22" s="28">
-        <v>3.5695437944302</v>
+        <v>3.6188240459995</v>
       </c>
       <c r="S22" s="28">
-        <v>3.5216169712727</v>
+        <v>3.6315882846847</v>
       </c>
       <c r="T22" s="28">
-        <v>3.5606907079504</v>
+        <v>3.5458888554717</v>
       </c>
       <c r="U22" s="28">
-        <v>2.7203374426976</v>
+        <v>2.7553951429907</v>
       </c>
       <c r="V22" s="28">
-        <v>3.3266582598043</v>
+        <v>3.3518219115298</v>
       </c>
       <c r="W22" s="28">
-        <v>2.7791637945968</v>
+        <v>2.853340893642</v>
       </c>
       <c r="X22" s="28">
-        <v>2.7911323232245</v>
+        <v>2.8366732550699</v>
       </c>
       <c r="Y22" s="28">
-        <v>2.8554728040829</v>
+        <v>2.831604104833</v>
       </c>
       <c r="Z22" s="28">
-        <v>2.8778307836256</v>
+        <v>2.7627322683109</v>
       </c>
       <c r="AA22" s="28">
-        <v>2.9245810877719</v>
+        <v>2.8030101516027</v>
       </c>
       <c r="AB22" s="28">
-        <v>2.2806356012591</v>
+        <v>2.2198538821648</v>
       </c>
       <c r="AC22" s="28">
-        <v>3.1565517773356</v>
+        <v>3.0428811985329</v>
       </c>
       <c r="AD22" s="28">
-        <v>3.0910364109133</v>
+        <v>3.0011513275093</v>
       </c>
       <c r="AE22" s="28">
-        <v>3.0690457165938</v>
+        <v>2.9843223156703</v>
       </c>
       <c r="AF22" s="41">
-        <v>5.088764808729</v>
+        <v>4.9433742841649</v>
       </c>
     </row>
     <row r="23" spans="1:32">
@@ -13632,1936 +14690,6 @@
         <v>2</v>
       </c>
       <c r="C24" s="24">
-        <v>85.871964679912</v>
-      </c>
-      <c r="D24" s="24">
-        <v>84.752311301228</v>
-      </c>
-      <c r="E24" s="24">
-        <v>84.875051774127</v>
-      </c>
-      <c r="F24" s="24">
-        <v>84.993323203021</v>
-      </c>
-      <c r="G24" s="24">
-        <v>85.098811498065</v>
-      </c>
-      <c r="H24" s="24">
-        <v>84.60389879718</v>
-      </c>
-      <c r="I24" s="24">
-        <v>84.315624423538</v>
-      </c>
-      <c r="J24" s="24">
-        <v>84.206986588598</v>
-      </c>
-      <c r="K24" s="24">
-        <v>83.404903726278</v>
-      </c>
-      <c r="L24" s="24">
-        <v>83.236313236313</v>
-      </c>
-      <c r="M24" s="24">
-        <v>82.550025417071</v>
-      </c>
-      <c r="N24" s="24">
-        <v>82.000693481276</v>
-      </c>
-      <c r="O24" s="24">
-        <v>81.453536754508</v>
-      </c>
-      <c r="P24" s="24">
-        <v>81.450120303535</v>
-      </c>
-      <c r="Q24" s="24">
-        <v>81.730387879749</v>
-      </c>
-      <c r="R24" s="24">
-        <v>84.418830717956</v>
-      </c>
-      <c r="S24" s="24">
-        <v>84.743055555556</v>
-      </c>
-      <c r="T24" s="24">
-        <v>84.176394293126</v>
-      </c>
-      <c r="U24" s="24">
-        <v>84.603891591383</v>
-      </c>
-      <c r="V24" s="24">
-        <v>85.159138290479</v>
-      </c>
-      <c r="W24" s="24">
-        <v>85.560035219426</v>
-      </c>
-      <c r="X24" s="24">
-        <v>85.887096774194</v>
-      </c>
-      <c r="Y24" s="24">
-        <v>86.588759042849</v>
-      </c>
-      <c r="Z24" s="24">
-        <v>85.796798886569</v>
-      </c>
-      <c r="AA24" s="24">
-        <v>85.278009839413</v>
-      </c>
-      <c r="AB24" s="24">
-        <v>84.692811368069</v>
-      </c>
-      <c r="AC24" s="24">
-        <v>83.644221385752</v>
-      </c>
-      <c r="AD24" s="24">
-        <v>83.170595620031</v>
-      </c>
-      <c r="AE24" s="24">
-        <v>82.961205693553</v>
-      </c>
-      <c r="AF24" s="37">
-        <v>83.072625698324</v>
-      </c>
-    </row>
-    <row r="25" spans="1:32">
-      <c r="A25" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="B25" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="C25" s="30">
-        <v>2.3038724341418</v>
-      </c>
-      <c r="D25" s="30">
-        <v>2.3400103311714</v>
-      </c>
-      <c r="E25" s="30">
-        <v>2.3259151755468</v>
-      </c>
-      <c r="F25" s="30">
-        <v>2.3148078033451</v>
-      </c>
-      <c r="G25" s="30">
-        <v>2.1530285223282</v>
-      </c>
-      <c r="H25" s="30">
-        <v>2.201671031729</v>
-      </c>
-      <c r="I25" s="30">
-        <v>2.2344673555998</v>
-      </c>
-      <c r="J25" s="30">
-        <v>2.2561069268727</v>
-      </c>
-      <c r="K25" s="30">
-        <v>2.3610566235125</v>
-      </c>
-      <c r="L25" s="30">
-        <v>2.3612695759602</v>
-      </c>
-      <c r="M25" s="30">
-        <v>2.3811175996286</v>
-      </c>
-      <c r="N25" s="30">
-        <v>2.2196646862358</v>
-      </c>
-      <c r="O25" s="30">
-        <v>2.2718760561376</v>
-      </c>
-      <c r="P25" s="30">
-        <v>2.2983490589388</v>
-      </c>
-      <c r="Q25" s="30">
-        <v>2.3146121979433</v>
-      </c>
-      <c r="R25" s="30">
-        <v>2.3819318915661</v>
-      </c>
-      <c r="S25" s="30">
-        <v>2.3657003556842</v>
-      </c>
-      <c r="T25" s="30">
-        <v>2.3638622722965</v>
-      </c>
-      <c r="U25" s="30">
-        <v>2.1804162484776</v>
-      </c>
-      <c r="V25" s="30">
-        <v>2.1899938753637</v>
-      </c>
-      <c r="W25" s="30">
-        <v>2.196313309887</v>
-      </c>
-      <c r="X25" s="30">
-        <v>2.2021523587948</v>
-      </c>
-      <c r="Y25" s="30">
-        <v>2.2879846166898</v>
-      </c>
-      <c r="Z25" s="30">
-        <v>2.2968147711704</v>
-      </c>
-      <c r="AA25" s="30">
-        <v>2.3120109974936</v>
-      </c>
-      <c r="AB25" s="30">
-        <v>2.1663271957276</v>
-      </c>
-      <c r="AC25" s="30">
-        <v>2.2298502359697</v>
-      </c>
-      <c r="AD25" s="30">
-        <v>2.2655462184874</v>
-      </c>
-      <c r="AE25" s="30">
-        <v>2.2890073934776</v>
-      </c>
-      <c r="AF25" s="44">
-        <v>2.4134085738235</v>
-      </c>
-    </row>
-    <row r="26" spans="1:32">
-      <c r="A26" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="B26" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="C26" s="29">
-        <v>2.9017921466103</v>
-      </c>
-      <c r="D26" s="29">
-        <v>2.947563085722</v>
-      </c>
-      <c r="E26" s="29">
-        <v>2.9382338639474</v>
-      </c>
-      <c r="F26" s="29">
-        <v>2.9068425728896</v>
-      </c>
-      <c r="G26" s="29">
-        <v>2.7257874801044</v>
-      </c>
-      <c r="H26" s="29">
-        <v>2.7756711246138</v>
-      </c>
-      <c r="I26" s="29">
-        <v>2.8093237789976</v>
-      </c>
-      <c r="J26" s="29">
-        <v>2.8311156194695</v>
-      </c>
-      <c r="K26" s="29">
-        <v>2.9303505680015</v>
-      </c>
-      <c r="L26" s="29">
-        <v>2.9319416547176</v>
-      </c>
-      <c r="M26" s="29">
-        <v>2.957110060472</v>
-      </c>
-      <c r="N26" s="29">
-        <v>2.7533674116319</v>
-      </c>
-      <c r="O26" s="29">
-        <v>2.818598493034</v>
-      </c>
-      <c r="P26" s="29">
-        <v>2.8573547444651</v>
-      </c>
-      <c r="Q26" s="29">
-        <v>2.8802218068247</v>
-      </c>
-      <c r="R26" s="29">
-        <v>3.5695437944302</v>
-      </c>
-      <c r="S26" s="29">
-        <v>3.5454220422177</v>
-      </c>
-      <c r="T26" s="29">
-        <v>3.5504382506115</v>
-      </c>
-      <c r="U26" s="29">
-        <v>3.3398036209933</v>
-      </c>
-      <c r="V26" s="29">
-        <v>3.337093956197</v>
-      </c>
-      <c r="W26" s="29">
-        <v>3.2417455163347</v>
-      </c>
-      <c r="X26" s="29">
-        <v>3.1762312271085</v>
-      </c>
-      <c r="Y26" s="29">
-        <v>2.8554728040829</v>
-      </c>
-      <c r="Z26" s="29">
-        <v>2.8666055285224</v>
-      </c>
-      <c r="AA26" s="29">
-        <v>2.8856659750051</v>
-      </c>
-      <c r="AB26" s="29">
-        <v>2.7378961298995</v>
-      </c>
-      <c r="AC26" s="29">
-        <v>2.8168278376808</v>
-      </c>
-      <c r="AD26" s="29">
-        <v>2.8610760755556</v>
-      </c>
-      <c r="AE26" s="29">
-        <v>2.8901386948028</v>
-      </c>
-      <c r="AF26" s="43">
-        <v>5.088764808729</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells>
-    <mergeCell ref="A1:AF1"/>
-    <mergeCell ref="C6:C6"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="K6:Q6"/>
-    <mergeCell ref="R6:X6"/>
-    <mergeCell ref="Y6:AE6"/>
-    <mergeCell ref="AF6:AF6"/>
-    <mergeCell ref="A23:AF23"/>
-  </mergeCells>
-  <printOptions gridLines="false" gridLinesSet="true"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="landscape" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <tableParts count="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:AF26"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col min="1" max="1" width="24" customWidth="true" style="0"/>
-    <col min="2" max="2" width="3" customWidth="true" style="0"/>
-    <col min="3" max="3" width="11" customWidth="true" style="0"/>
-    <col min="4" max="4" width="11" customWidth="true" style="0"/>
-    <col min="5" max="5" width="11" customWidth="true" style="0"/>
-    <col min="6" max="6" width="11" customWidth="true" style="0"/>
-    <col min="7" max="7" width="11" customWidth="true" style="0"/>
-    <col min="8" max="8" width="11" customWidth="true" style="0"/>
-    <col min="9" max="9" width="11" customWidth="true" style="0"/>
-    <col min="10" max="10" width="11" customWidth="true" style="0"/>
-    <col min="11" max="11" width="11" customWidth="true" style="0"/>
-    <col min="12" max="12" width="11" customWidth="true" style="0"/>
-    <col min="13" max="13" width="11" customWidth="true" style="0"/>
-    <col min="14" max="14" width="11" customWidth="true" style="0"/>
-    <col min="15" max="15" width="11" customWidth="true" style="0"/>
-    <col min="16" max="16" width="11" customWidth="true" style="0"/>
-    <col min="17" max="17" width="11" customWidth="true" style="0"/>
-    <col min="18" max="18" width="11" customWidth="true" style="0"/>
-    <col min="19" max="19" width="11" customWidth="true" style="0"/>
-    <col min="20" max="20" width="11" customWidth="true" style="0"/>
-    <col min="21" max="21" width="11" customWidth="true" style="0"/>
-    <col min="22" max="22" width="11" customWidth="true" style="0"/>
-    <col min="23" max="23" width="11" customWidth="true" style="0"/>
-    <col min="24" max="24" width="11" customWidth="true" style="0"/>
-    <col min="25" max="25" width="11" customWidth="true" style="0"/>
-    <col min="26" max="26" width="11" customWidth="true" style="0"/>
-    <col min="27" max="27" width="11" customWidth="true" style="0"/>
-    <col min="28" max="28" width="11" customWidth="true" style="0"/>
-    <col min="29" max="29" width="11" customWidth="true" style="0"/>
-    <col min="30" max="30" width="11" customWidth="true" style="0"/>
-    <col min="31" max="31" width="11" customWidth="true" style="0"/>
-    <col min="32" max="32" width="11" customWidth="true" style="0"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:32" customHeight="1" ht="28">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
-      <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
-      <c r="W1" s="1"/>
-      <c r="X1" s="1"/>
-      <c r="Y1" s="1"/>
-      <c r="Z1" s="1"/>
-      <c r="AA1" s="1"/>
-      <c r="AB1" s="1"/>
-      <c r="AC1" s="1"/>
-      <c r="AD1" s="1"/>
-      <c r="AE1" s="1"/>
-      <c r="AF1" s="1"/>
-    </row>
-    <row r="2" spans="1:32">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="3" spans="1:32">
-      <c r="A3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="5">
-        <v>45852.0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:32">
-      <c r="A4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="6" spans="1:32" customHeight="1" ht="26">
-      <c r="A6" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>219</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>220</v>
-      </c>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="8" t="s">
-        <v>221</v>
-      </c>
-      <c r="L6" s="8"/>
-      <c r="M6" s="8"/>
-      <c r="N6" s="8"/>
-      <c r="O6" s="8"/>
-      <c r="P6" s="8"/>
-      <c r="Q6" s="8"/>
-      <c r="R6" s="8" t="s">
-        <v>222</v>
-      </c>
-      <c r="S6" s="8"/>
-      <c r="T6" s="8"/>
-      <c r="U6" s="8"/>
-      <c r="V6" s="8"/>
-      <c r="W6" s="8"/>
-      <c r="X6" s="8"/>
-      <c r="Y6" s="8" t="s">
-        <v>223</v>
-      </c>
-      <c r="Z6" s="8"/>
-      <c r="AA6" s="8"/>
-      <c r="AB6" s="8"/>
-      <c r="AC6" s="8"/>
-      <c r="AD6" s="8"/>
-      <c r="AE6" s="8"/>
-      <c r="AF6" s="11" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="7" spans="1:32" customHeight="1" ht="36">
-      <c r="A7" s="7"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>190</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>191</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>192</v>
-      </c>
-      <c r="H7" s="10" t="s">
-        <v>193</v>
-      </c>
-      <c r="I7" s="10" t="s">
-        <v>194</v>
-      </c>
-      <c r="J7" s="10" t="s">
-        <v>195</v>
-      </c>
-      <c r="K7" s="10" t="s">
-        <v>196</v>
-      </c>
-      <c r="L7" s="10" t="s">
-        <v>197</v>
-      </c>
-      <c r="M7" s="10" t="s">
-        <v>198</v>
-      </c>
-      <c r="N7" s="10" t="s">
-        <v>199</v>
-      </c>
-      <c r="O7" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="P7" s="10" t="s">
-        <v>201</v>
-      </c>
-      <c r="Q7" s="10" t="s">
-        <v>202</v>
-      </c>
-      <c r="R7" s="10" t="s">
-        <v>203</v>
-      </c>
-      <c r="S7" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="T7" s="10" t="s">
-        <v>205</v>
-      </c>
-      <c r="U7" s="10" t="s">
-        <v>206</v>
-      </c>
-      <c r="V7" s="10" t="s">
-        <v>207</v>
-      </c>
-      <c r="W7" s="10" t="s">
-        <v>208</v>
-      </c>
-      <c r="X7" s="10" t="s">
-        <v>209</v>
-      </c>
-      <c r="Y7" s="10" t="s">
-        <v>210</v>
-      </c>
-      <c r="Z7" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="AA7" s="10" t="s">
-        <v>212</v>
-      </c>
-      <c r="AB7" s="10" t="s">
-        <v>213</v>
-      </c>
-      <c r="AC7" s="10" t="s">
-        <v>214</v>
-      </c>
-      <c r="AD7" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="AE7" s="10" t="s">
-        <v>216</v>
-      </c>
-      <c r="AF7" s="12" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="8" spans="1:32">
-      <c r="A8" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="C8" s="19">
-        <v>1.0</v>
-      </c>
-      <c r="D8" s="19">
-        <v>1.0</v>
-      </c>
-      <c r="E8" s="19">
-        <v>4.0</v>
-      </c>
-      <c r="F8" s="19">
-        <v>3.0</v>
-      </c>
-      <c r="G8" s="19"/>
-      <c r="H8" s="19">
-        <v>2.0</v>
-      </c>
-      <c r="I8" s="19">
-        <v>2.0</v>
-      </c>
-      <c r="J8" s="19">
-        <v>2.0</v>
-      </c>
-      <c r="K8" s="19">
-        <v>2.0</v>
-      </c>
-      <c r="L8" s="19">
-        <v>4.0</v>
-      </c>
-      <c r="M8" s="19">
-        <v>3.0</v>
-      </c>
-      <c r="N8" s="19">
-        <v>3.0</v>
-      </c>
-      <c r="O8" s="19">
-        <v>2.0</v>
-      </c>
-      <c r="P8" s="19">
-        <v>4.0</v>
-      </c>
-      <c r="Q8" s="19"/>
-      <c r="R8" s="19">
-        <v>2.0</v>
-      </c>
-      <c r="S8" s="19">
-        <v>1.0</v>
-      </c>
-      <c r="T8" s="19">
-        <v>2.0</v>
-      </c>
-      <c r="U8" s="19">
-        <v>2.0</v>
-      </c>
-      <c r="V8" s="19"/>
-      <c r="W8" s="19">
-        <v>1.0</v>
-      </c>
-      <c r="X8" s="19"/>
-      <c r="Y8" s="19">
-        <v>2.0</v>
-      </c>
-      <c r="Z8" s="19">
-        <v>1.0</v>
-      </c>
-      <c r="AA8" s="19">
-        <v>3.0</v>
-      </c>
-      <c r="AB8" s="19">
-        <v>1.0</v>
-      </c>
-      <c r="AC8" s="19">
-        <v>2.0</v>
-      </c>
-      <c r="AD8" s="19">
-        <v>3.0</v>
-      </c>
-      <c r="AE8" s="19">
-        <v>2.0</v>
-      </c>
-      <c r="AF8" s="32">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:32">
-      <c r="A9" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="C9" s="20"/>
-      <c r="D9" s="20"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="20"/>
-      <c r="I9" s="20"/>
-      <c r="J9" s="20"/>
-      <c r="K9" s="20"/>
-      <c r="L9" s="20"/>
-      <c r="M9" s="20"/>
-      <c r="N9" s="20"/>
-      <c r="O9" s="20"/>
-      <c r="P9" s="20"/>
-      <c r="Q9" s="20"/>
-      <c r="R9" s="20"/>
-      <c r="S9" s="20"/>
-      <c r="T9" s="20"/>
-      <c r="U9" s="20"/>
-      <c r="V9" s="20"/>
-      <c r="W9" s="20"/>
-      <c r="X9" s="20"/>
-      <c r="Y9" s="20"/>
-      <c r="Z9" s="20"/>
-      <c r="AA9" s="20"/>
-      <c r="AB9" s="20"/>
-      <c r="AC9" s="20"/>
-      <c r="AD9" s="20"/>
-      <c r="AE9" s="20"/>
-      <c r="AF9" s="33"/>
-    </row>
-    <row r="10" spans="1:32">
-      <c r="A10" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="B10" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="C10" s="19">
-        <v>6311.0</v>
-      </c>
-      <c r="D10" s="19">
-        <v>6330.0</v>
-      </c>
-      <c r="E10" s="19">
-        <v>6324.0</v>
-      </c>
-      <c r="F10" s="19">
-        <v>6329.0</v>
-      </c>
-      <c r="G10" s="19">
-        <v>6290.0</v>
-      </c>
-      <c r="H10" s="19">
-        <v>6163.0</v>
-      </c>
-      <c r="I10" s="19">
-        <v>6085.0</v>
-      </c>
-      <c r="J10" s="19">
-        <v>6108.0</v>
-      </c>
-      <c r="K10" s="19">
-        <v>6161.0</v>
-      </c>
-      <c r="L10" s="19">
-        <v>6154.0</v>
-      </c>
-      <c r="M10" s="19">
-        <v>6176.0</v>
-      </c>
-      <c r="N10" s="19">
-        <v>6020.0</v>
-      </c>
-      <c r="O10" s="19">
-        <v>5844.0</v>
-      </c>
-      <c r="P10" s="19">
-        <v>5841.0</v>
-      </c>
-      <c r="Q10" s="19">
-        <v>5954.0</v>
-      </c>
-      <c r="R10" s="19">
-        <v>6077.0</v>
-      </c>
-      <c r="S10" s="19">
-        <v>6158.0</v>
-      </c>
-      <c r="T10" s="19">
-        <v>6170.0</v>
-      </c>
-      <c r="U10" s="19">
-        <v>6236.0</v>
-      </c>
-      <c r="V10" s="19">
-        <v>6416.0</v>
-      </c>
-      <c r="W10" s="19">
-        <v>6515.0</v>
-      </c>
-      <c r="X10" s="19">
-        <v>6474.0</v>
-      </c>
-      <c r="Y10" s="19">
-        <v>6397.0</v>
-      </c>
-      <c r="Z10" s="19">
-        <v>6459.0</v>
-      </c>
-      <c r="AA10" s="19">
-        <v>6467.0</v>
-      </c>
-      <c r="AB10" s="19">
-        <v>6260.0</v>
-      </c>
-      <c r="AC10" s="19">
-        <v>6053.0</v>
-      </c>
-      <c r="AD10" s="19">
-        <v>6120.0</v>
-      </c>
-      <c r="AE10" s="19">
-        <v>6273.0</v>
-      </c>
-      <c r="AF10" s="32">
-        <v>6276.0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:32">
-      <c r="A11" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="B11" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="C11" s="21">
-        <v>396.53888888889</v>
-      </c>
-      <c r="D11" s="21">
-        <v>392.93333333333</v>
-      </c>
-      <c r="E11" s="21">
-        <v>386.76666666667</v>
-      </c>
-      <c r="F11" s="21">
-        <v>400.13888888889</v>
-      </c>
-      <c r="G11" s="21">
-        <v>395.35555555556</v>
-      </c>
-      <c r="H11" s="21">
-        <v>387.06111111111</v>
-      </c>
-      <c r="I11" s="21">
-        <v>384.59444444444</v>
-      </c>
-      <c r="J11" s="21">
-        <v>382.36666666667</v>
-      </c>
-      <c r="K11" s="21">
-        <v>389.17222222222</v>
-      </c>
-      <c r="L11" s="21">
-        <v>389.31111111111</v>
-      </c>
-      <c r="M11" s="21">
-        <v>394.88888888889</v>
-      </c>
-      <c r="N11" s="21">
-        <v>385.15555555556</v>
-      </c>
-      <c r="O11" s="21">
-        <v>364.43333333333</v>
-      </c>
-      <c r="P11" s="21">
-        <v>370.35</v>
-      </c>
-      <c r="Q11" s="21">
-        <v>375.22222222222</v>
-      </c>
-      <c r="R11" s="21">
-        <v>390.73888888889</v>
-      </c>
-      <c r="S11" s="21">
-        <v>389.28888888889</v>
-      </c>
-      <c r="T11" s="21">
-        <v>391.82222222222</v>
-      </c>
-      <c r="U11" s="21">
-        <v>397.85555555556</v>
-      </c>
-      <c r="V11" s="21">
-        <v>410.15555555556</v>
-      </c>
-      <c r="W11" s="21">
-        <v>404.20555555556</v>
-      </c>
-      <c r="X11" s="21">
-        <v>406.53333333333</v>
-      </c>
-      <c r="Y11" s="21">
-        <v>407.26111111111</v>
-      </c>
-      <c r="Z11" s="21">
-        <v>417.31666666667</v>
-      </c>
-      <c r="AA11" s="21">
-        <v>411.27222222222</v>
-      </c>
-      <c r="AB11" s="21">
-        <v>397.52222222222</v>
-      </c>
-      <c r="AC11" s="21">
-        <v>382.47222222222</v>
-      </c>
-      <c r="AD11" s="21">
-        <v>387.7</v>
-      </c>
-      <c r="AE11" s="21">
-        <v>389.75</v>
-      </c>
-      <c r="AF11" s="34">
-        <v>393.93333333333</v>
-      </c>
-    </row>
-    <row r="12" spans="1:32">
-      <c r="A12" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="B12" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="C12" s="22">
-        <v>62.832972411486</v>
-      </c>
-      <c r="D12" s="22">
-        <v>62.074776197999</v>
-      </c>
-      <c r="E12" s="22">
-        <v>61.158549441282</v>
-      </c>
-      <c r="F12" s="22">
-        <v>63.223082459929</v>
-      </c>
-      <c r="G12" s="22">
-        <v>62.854619325208</v>
-      </c>
-      <c r="H12" s="22">
-        <v>62.804009591289</v>
-      </c>
-      <c r="I12" s="22">
-        <v>63.203688487172</v>
-      </c>
-      <c r="J12" s="22">
-        <v>62.600960488976</v>
-      </c>
-      <c r="K12" s="22">
-        <v>63.167054410359</v>
-      </c>
-      <c r="L12" s="22">
-        <v>63.261474018705</v>
-      </c>
-      <c r="M12" s="22">
-        <v>63.939263097294</v>
-      </c>
-      <c r="N12" s="22">
-        <v>63.979328165375</v>
-      </c>
-      <c r="O12" s="22">
-        <v>62.36025553274</v>
-      </c>
-      <c r="P12" s="22">
-        <v>63.405238828968</v>
-      </c>
-      <c r="Q12" s="22">
-        <v>63.020191841153</v>
-      </c>
-      <c r="R12" s="22">
-        <v>64.297990602088</v>
-      </c>
-      <c r="S12" s="22">
-        <v>63.216773122587</v>
-      </c>
-      <c r="T12" s="22">
-        <v>63.504412029534</v>
-      </c>
-      <c r="U12" s="22">
-        <v>63.799800441879</v>
-      </c>
-      <c r="V12" s="22">
-        <v>63.926988085342</v>
-      </c>
-      <c r="W12" s="22">
-        <v>62.042295557261</v>
-      </c>
-      <c r="X12" s="22">
-        <v>62.794768818865</v>
-      </c>
-      <c r="Y12" s="22">
-        <v>63.66439129453</v>
-      </c>
-      <c r="Z12" s="22">
-        <v>64.610104763379</v>
-      </c>
-      <c r="AA12" s="22">
-        <v>63.595519131316</v>
-      </c>
-      <c r="AB12" s="22">
-        <v>63.501952431665</v>
-      </c>
-      <c r="AC12" s="22">
-        <v>63.187216623529</v>
-      </c>
-      <c r="AD12" s="22">
-        <v>63.349673202614</v>
-      </c>
-      <c r="AE12" s="22">
-        <v>62.131356607684</v>
-      </c>
-      <c r="AF12" s="35">
-        <v>62.768217548332</v>
-      </c>
-    </row>
-    <row r="13" spans="1:32">
-      <c r="A13" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="B13" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="C13" s="23">
-        <v>63.6</v>
-      </c>
-      <c r="D13" s="23">
-        <v>63.6</v>
-      </c>
-      <c r="E13" s="23">
-        <v>63.6</v>
-      </c>
-      <c r="F13" s="23">
-        <v>63.6</v>
-      </c>
-      <c r="G13" s="23">
-        <v>63.6</v>
-      </c>
-      <c r="H13" s="23">
-        <v>63.6</v>
-      </c>
-      <c r="I13" s="23">
-        <v>63.6</v>
-      </c>
-      <c r="J13" s="23">
-        <v>63.6</v>
-      </c>
-      <c r="K13" s="23">
-        <v>63.6</v>
-      </c>
-      <c r="L13" s="23">
-        <v>63.6</v>
-      </c>
-      <c r="M13" s="23">
-        <v>63.6</v>
-      </c>
-      <c r="N13" s="23">
-        <v>63.6</v>
-      </c>
-      <c r="O13" s="23">
-        <v>63.6</v>
-      </c>
-      <c r="P13" s="23">
-        <v>63.6</v>
-      </c>
-      <c r="Q13" s="23">
-        <v>63.6</v>
-      </c>
-      <c r="R13" s="23">
-        <v>63.6</v>
-      </c>
-      <c r="S13" s="23">
-        <v>63.6</v>
-      </c>
-      <c r="T13" s="23">
-        <v>63.6</v>
-      </c>
-      <c r="U13" s="23">
-        <v>63.6</v>
-      </c>
-      <c r="V13" s="23">
-        <v>63.6</v>
-      </c>
-      <c r="W13" s="23">
-        <v>63.6</v>
-      </c>
-      <c r="X13" s="23">
-        <v>63.6</v>
-      </c>
-      <c r="Y13" s="23">
-        <v>63.7</v>
-      </c>
-      <c r="Z13" s="23">
-        <v>63.7</v>
-      </c>
-      <c r="AA13" s="23">
-        <v>63.7</v>
-      </c>
-      <c r="AB13" s="23">
-        <v>63.7</v>
-      </c>
-      <c r="AC13" s="23">
-        <v>63.7</v>
-      </c>
-      <c r="AD13" s="23">
-        <v>63.7</v>
-      </c>
-      <c r="AE13" s="23">
-        <v>63.7</v>
-      </c>
-      <c r="AF13" s="36">
-        <v>63.7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:32">
-      <c r="A14" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="B14" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="C14" s="24">
-        <v>84.450689147598</v>
-      </c>
-      <c r="D14" s="24">
-        <v>84.716274089936</v>
-      </c>
-      <c r="E14" s="24">
-        <v>84.715338245144</v>
-      </c>
-      <c r="F14" s="24">
-        <v>84.816403109086</v>
-      </c>
-      <c r="G14" s="24">
-        <v>84.305052941965</v>
-      </c>
-      <c r="H14" s="24">
-        <v>82.625016758279</v>
-      </c>
-      <c r="I14" s="24">
-        <v>81.623071763917</v>
-      </c>
-      <c r="J14" s="24">
-        <v>81.953575741312</v>
-      </c>
-      <c r="K14" s="24">
-        <v>82.686887666085</v>
-      </c>
-      <c r="L14" s="24">
-        <v>82.637303612193</v>
-      </c>
-      <c r="M14" s="24">
-        <v>82.966147232671</v>
-      </c>
-      <c r="N14" s="24">
-        <v>80.903104421449</v>
-      </c>
-      <c r="O14" s="24">
-        <v>78.558946094905</v>
-      </c>
-      <c r="P14" s="24">
-        <v>78.560860793544</v>
-      </c>
-      <c r="Q14" s="24">
-        <v>80.080699394755</v>
-      </c>
-      <c r="R14" s="24">
-        <v>81.757029463205</v>
-      </c>
-      <c r="S14" s="24">
-        <v>82.857911733046</v>
-      </c>
-      <c r="T14" s="24">
-        <v>83.041722745626</v>
-      </c>
-      <c r="U14" s="24">
-        <v>83.952611739365</v>
-      </c>
-      <c r="V14" s="24">
-        <v>86.39913816321</v>
-      </c>
-      <c r="W14" s="24">
-        <v>87.744107744108</v>
-      </c>
-      <c r="X14" s="24">
-        <v>87.191919191919</v>
-      </c>
-      <c r="Y14" s="24">
-        <v>86.178095109794</v>
-      </c>
-      <c r="Z14" s="24">
-        <v>87.025060630558</v>
-      </c>
-      <c r="AA14" s="24">
-        <v>87.168081951746</v>
-      </c>
-      <c r="AB14" s="24">
-        <v>84.400701092086</v>
-      </c>
-      <c r="AC14" s="24">
-        <v>81.631827376939</v>
-      </c>
-      <c r="AD14" s="24">
-        <v>82.56880733945</v>
-      </c>
-      <c r="AE14" s="24">
-        <v>84.655870445344</v>
-      </c>
-      <c r="AF14" s="37">
-        <v>84.73066018631</v>
-      </c>
-    </row>
-    <row r="15" spans="1:32">
-      <c r="A15" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="B15" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="C15" s="25">
-        <v>84.750968086527</v>
-      </c>
-      <c r="D15" s="25">
-        <v>84.448897795591</v>
-      </c>
-      <c r="E15" s="25">
-        <v>86.531266702298</v>
-      </c>
-      <c r="F15" s="25">
-        <v>86.500935578722</v>
-      </c>
-      <c r="G15" s="25">
-        <v>84.810803583367</v>
-      </c>
-      <c r="H15" s="25">
-        <v>83.828250401284</v>
-      </c>
-      <c r="I15" s="25">
-        <v>84.037998394434</v>
-      </c>
-      <c r="J15" s="25">
-        <v>84.450689147598</v>
-      </c>
-      <c r="K15" s="25">
-        <v>84.716274089936</v>
-      </c>
-      <c r="L15" s="25">
-        <v>84.715338245144</v>
-      </c>
-      <c r="M15" s="25">
-        <v>84.816403109086</v>
-      </c>
-      <c r="N15" s="25">
-        <v>84.305052941965</v>
-      </c>
-      <c r="O15" s="25">
-        <v>82.625016758279</v>
-      </c>
-      <c r="P15" s="25">
-        <v>81.623071763917</v>
-      </c>
-      <c r="Q15" s="25">
-        <v>81.953575741312</v>
-      </c>
-      <c r="R15" s="25">
-        <v>82.686887666085</v>
-      </c>
-      <c r="S15" s="25">
-        <v>82.637303612193</v>
-      </c>
-      <c r="T15" s="25">
-        <v>82.966147232671</v>
-      </c>
-      <c r="U15" s="25">
-        <v>80.903104421449</v>
-      </c>
-      <c r="V15" s="25">
-        <v>78.558946094905</v>
-      </c>
-      <c r="W15" s="25">
-        <v>78.560860793544</v>
-      </c>
-      <c r="X15" s="25">
-        <v>80.080699394755</v>
-      </c>
-      <c r="Y15" s="25">
-        <v>81.757029463205</v>
-      </c>
-      <c r="Z15" s="25">
-        <v>82.857911733046</v>
-      </c>
-      <c r="AA15" s="25">
-        <v>83.041722745626</v>
-      </c>
-      <c r="AB15" s="25">
-        <v>83.952611739365</v>
-      </c>
-      <c r="AC15" s="25">
-        <v>86.39913816321</v>
-      </c>
-      <c r="AD15" s="25">
-        <v>87.744107744108</v>
-      </c>
-      <c r="AE15" s="25">
-        <v>87.191919191919</v>
-      </c>
-      <c r="AF15" s="38">
-        <v>86.178095109794</v>
-      </c>
-    </row>
-    <row r="16" spans="1:32">
-      <c r="A16" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="B16" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="C16" s="26">
-        <v>93.0</v>
-      </c>
-      <c r="D16" s="26">
-        <v>92.0</v>
-      </c>
-      <c r="E16" s="26">
-        <v>92.0</v>
-      </c>
-      <c r="F16" s="26">
-        <v>92.0</v>
-      </c>
-      <c r="G16" s="26">
-        <v>92.0</v>
-      </c>
-      <c r="H16" s="26">
-        <v>92.0</v>
-      </c>
-      <c r="I16" s="26">
-        <v>92.0</v>
-      </c>
-      <c r="J16" s="26">
-        <v>92.0</v>
-      </c>
-      <c r="K16" s="26">
-        <v>92.0</v>
-      </c>
-      <c r="L16" s="26">
-        <v>92.0</v>
-      </c>
-      <c r="M16" s="26">
-        <v>92.0</v>
-      </c>
-      <c r="N16" s="26">
-        <v>92.0</v>
-      </c>
-      <c r="O16" s="26">
-        <v>92.0</v>
-      </c>
-      <c r="P16" s="26">
-        <v>92.0</v>
-      </c>
-      <c r="Q16" s="26">
-        <v>92.0</v>
-      </c>
-      <c r="R16" s="26">
-        <v>92.0</v>
-      </c>
-      <c r="S16" s="26">
-        <v>92.0</v>
-      </c>
-      <c r="T16" s="26">
-        <v>92.0</v>
-      </c>
-      <c r="U16" s="26">
-        <v>92.0</v>
-      </c>
-      <c r="V16" s="26">
-        <v>92.0</v>
-      </c>
-      <c r="W16" s="26">
-        <v>92.0</v>
-      </c>
-      <c r="X16" s="26">
-        <v>92.0</v>
-      </c>
-      <c r="Y16" s="26">
-        <v>92.0</v>
-      </c>
-      <c r="Z16" s="26">
-        <v>92.0</v>
-      </c>
-      <c r="AA16" s="26">
-        <v>92.0</v>
-      </c>
-      <c r="AB16" s="26">
-        <v>92.0</v>
-      </c>
-      <c r="AC16" s="26">
-        <v>92.0</v>
-      </c>
-      <c r="AD16" s="26">
-        <v>92.0</v>
-      </c>
-      <c r="AE16" s="26">
-        <v>92.0</v>
-      </c>
-      <c r="AF16" s="39">
-        <v>91.0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:32">
-      <c r="A17" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="B17" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="C17" s="21">
-        <v>934.25</v>
-      </c>
-      <c r="D17" s="21">
-        <v>934.125</v>
-      </c>
-      <c r="E17" s="21">
-        <v>934.0</v>
-      </c>
-      <c r="F17" s="21">
-        <v>933.125</v>
-      </c>
-      <c r="G17" s="21">
-        <v>671.58</v>
-      </c>
-      <c r="H17" s="21">
-        <v>932.625</v>
-      </c>
-      <c r="I17" s="21">
-        <v>932.375</v>
-      </c>
-      <c r="J17" s="21">
-        <v>931.875</v>
-      </c>
-      <c r="K17" s="21">
-        <v>931.625</v>
-      </c>
-      <c r="L17" s="21">
-        <v>931.375</v>
-      </c>
-      <c r="M17" s="21">
-        <v>930.875</v>
-      </c>
-      <c r="N17" s="21">
-        <v>669.96</v>
-      </c>
-      <c r="O17" s="21">
-        <v>930.125</v>
-      </c>
-      <c r="P17" s="21">
-        <v>930.125</v>
-      </c>
-      <c r="Q17" s="21">
-        <v>951.936</v>
-      </c>
-      <c r="R17" s="21">
-        <v>475.84</v>
-      </c>
-      <c r="S17" s="21">
-        <v>475.712</v>
-      </c>
-      <c r="T17" s="21">
-        <v>464.5</v>
-      </c>
-      <c r="U17" s="21">
-        <v>668.7</v>
-      </c>
-      <c r="V17" s="21">
-        <v>928.5</v>
-      </c>
-      <c r="W17" s="21">
-        <v>928.25</v>
-      </c>
-      <c r="X17" s="21">
-        <v>928.125</v>
-      </c>
-      <c r="Y17" s="21">
-        <v>928.125</v>
-      </c>
-      <c r="Z17" s="21">
-        <v>927.875</v>
-      </c>
-      <c r="AA17" s="21">
-        <v>927.75</v>
-      </c>
-      <c r="AB17" s="21">
-        <v>667.71</v>
-      </c>
-      <c r="AC17" s="21">
-        <v>927.125</v>
-      </c>
-      <c r="AD17" s="21">
-        <v>926.875</v>
-      </c>
-      <c r="AE17" s="21">
-        <v>926.5</v>
-      </c>
-      <c r="AF17" s="34">
-        <v>926.25</v>
-      </c>
-    </row>
-    <row r="18" spans="1:32">
-      <c r="A18" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="B18" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="C18" s="19">
-        <v>7202.0</v>
-      </c>
-      <c r="D18" s="19">
-        <v>7202.0</v>
-      </c>
-      <c r="E18" s="19">
-        <v>7202.0</v>
-      </c>
-      <c r="F18" s="19">
-        <v>7202.0</v>
-      </c>
-      <c r="G18" s="19">
-        <v>7202.0</v>
-      </c>
-      <c r="H18" s="19">
-        <v>7202.0</v>
-      </c>
-      <c r="I18" s="19">
-        <v>7202.0</v>
-      </c>
-      <c r="J18" s="19">
-        <v>7202.0</v>
-      </c>
-      <c r="K18" s="19">
-        <v>7402.0</v>
-      </c>
-      <c r="L18" s="19">
-        <v>7402.0</v>
-      </c>
-      <c r="M18" s="19">
-        <v>7402.0</v>
-      </c>
-      <c r="N18" s="19">
-        <v>7402.0</v>
-      </c>
-      <c r="O18" s="19">
-        <v>7402.0</v>
-      </c>
-      <c r="P18" s="19">
-        <v>7402.0</v>
-      </c>
-      <c r="Q18" s="19">
-        <v>7402.0</v>
-      </c>
-      <c r="R18" s="19">
-        <v>7402.0</v>
-      </c>
-      <c r="S18" s="19">
-        <v>7402.0</v>
-      </c>
-      <c r="T18" s="19">
-        <v>7401.0</v>
-      </c>
-      <c r="U18" s="19">
-        <v>7401.0</v>
-      </c>
-      <c r="V18" s="19">
-        <v>7401.0</v>
-      </c>
-      <c r="W18" s="19">
-        <v>7401.0</v>
-      </c>
-      <c r="X18" s="19">
-        <v>7401.0</v>
-      </c>
-      <c r="Y18" s="19">
-        <v>7401.0</v>
-      </c>
-      <c r="Z18" s="19">
-        <v>7401.0</v>
-      </c>
-      <c r="AA18" s="19">
-        <v>7401.0</v>
-      </c>
-      <c r="AB18" s="19">
-        <v>7401.0</v>
-      </c>
-      <c r="AC18" s="19">
-        <v>7401.0</v>
-      </c>
-      <c r="AD18" s="19">
-        <v>7401.0</v>
-      </c>
-      <c r="AE18" s="19">
-        <v>7401.0</v>
-      </c>
-      <c r="AF18" s="32">
-        <v>7401.0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:32">
-      <c r="A19" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="B19" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="C19" s="21"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="21"/>
-      <c r="I19" s="21"/>
-      <c r="J19" s="21"/>
-      <c r="K19" s="21"/>
-      <c r="L19" s="21"/>
-      <c r="M19" s="21"/>
-      <c r="N19" s="21"/>
-      <c r="O19" s="21"/>
-      <c r="P19" s="21"/>
-      <c r="Q19" s="21"/>
-      <c r="R19" s="21">
-        <v>475.84</v>
-      </c>
-      <c r="S19" s="21">
-        <v>475.712</v>
-      </c>
-      <c r="T19" s="21">
-        <v>464.5</v>
-      </c>
-      <c r="U19" s="21"/>
-      <c r="V19" s="21"/>
-      <c r="W19" s="21"/>
-      <c r="X19" s="21"/>
-      <c r="Y19" s="21"/>
-      <c r="Z19" s="21"/>
-      <c r="AA19" s="21"/>
-      <c r="AB19" s="21"/>
-      <c r="AC19" s="21"/>
-      <c r="AD19" s="21"/>
-      <c r="AE19" s="21"/>
-      <c r="AF19" s="34"/>
-    </row>
-    <row r="20" spans="1:32">
-      <c r="A20" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="B20" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="C20" s="19"/>
-      <c r="D20" s="19"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="19"/>
-      <c r="G20" s="19"/>
-      <c r="H20" s="19"/>
-      <c r="I20" s="19"/>
-      <c r="J20" s="19"/>
-      <c r="K20" s="19"/>
-      <c r="L20" s="19"/>
-      <c r="M20" s="19"/>
-      <c r="N20" s="19"/>
-      <c r="O20" s="19"/>
-      <c r="P20" s="19"/>
-      <c r="Q20" s="19"/>
-      <c r="R20" s="19">
-        <v>7532.0</v>
-      </c>
-      <c r="S20" s="19">
-        <v>7532.0</v>
-      </c>
-      <c r="T20" s="19">
-        <v>7532.0</v>
-      </c>
-      <c r="U20" s="19">
-        <v>7532.0</v>
-      </c>
-      <c r="V20" s="19">
-        <v>7532.0</v>
-      </c>
-      <c r="W20" s="19">
-        <v>7532.0</v>
-      </c>
-      <c r="X20" s="19">
-        <v>7531.0</v>
-      </c>
-      <c r="Y20" s="19">
-        <v>7531.0</v>
-      </c>
-      <c r="Z20" s="19">
-        <v>7531.0</v>
-      </c>
-      <c r="AA20" s="19">
-        <v>7531.0</v>
-      </c>
-      <c r="AB20" s="19">
-        <v>7531.0</v>
-      </c>
-      <c r="AC20" s="19">
-        <v>7531.0</v>
-      </c>
-      <c r="AD20" s="19">
-        <v>7531.0</v>
-      </c>
-      <c r="AE20" s="19">
-        <v>7531.0</v>
-      </c>
-      <c r="AF20" s="32">
-        <v>7531.0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:32">
-      <c r="A21" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="B21" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="C21" s="30">
-        <v>2.3560110399709</v>
-      </c>
-      <c r="D21" s="30">
-        <v>2.3773116728877</v>
-      </c>
-      <c r="E21" s="30">
-        <v>2.4148927001638</v>
-      </c>
-      <c r="F21" s="30">
-        <v>2.3320027768136</v>
-      </c>
-      <c r="G21" s="30">
-        <v>1.6986734865943</v>
-      </c>
-      <c r="H21" s="30">
-        <v>2.4095032366408</v>
-      </c>
-      <c r="I21" s="30">
-        <v>2.4243069900472</v>
-      </c>
-      <c r="J21" s="30">
-        <v>2.4371240519571</v>
-      </c>
-      <c r="K21" s="30">
-        <v>2.3938630426404</v>
-      </c>
-      <c r="L21" s="30">
-        <v>2.392366858839</v>
-      </c>
-      <c r="M21" s="30">
-        <v>2.3573086662915</v>
-      </c>
-      <c r="N21" s="30">
-        <v>1.7394530348488</v>
-      </c>
-      <c r="O21" s="27">
-        <v>2.5522500685997</v>
-      </c>
-      <c r="P21" s="27">
-        <v>2.5114756311597</v>
-      </c>
-      <c r="Q21" s="27">
-        <v>2.5369925969796</v>
-      </c>
-      <c r="R21" s="30">
-        <v>2.4355906900033</v>
-      </c>
-      <c r="S21" s="30">
-        <v>2.4440050234045</v>
-      </c>
-      <c r="T21" s="30">
-        <v>2.37097323049</v>
-      </c>
-      <c r="U21" s="30">
-        <v>1.6807607451057</v>
-      </c>
-      <c r="V21" s="30">
-        <v>2.2637752614184</v>
-      </c>
-      <c r="W21" s="30">
-        <v>2.2964800637739</v>
-      </c>
-      <c r="X21" s="30">
-        <v>2.2830231223352</v>
-      </c>
-      <c r="Y21" s="30">
-        <v>2.2789433478385</v>
-      </c>
-      <c r="Z21" s="30">
-        <v>2.2234314469428</v>
-      </c>
-      <c r="AA21" s="30">
-        <v>2.2558051574383</v>
-      </c>
-      <c r="AB21" s="30">
-        <v>1.6796796824776</v>
-      </c>
-      <c r="AC21" s="30">
-        <v>2.4240322463505</v>
-      </c>
-      <c r="AD21" s="30">
-        <v>2.3907015733815</v>
-      </c>
-      <c r="AE21" s="30">
-        <v>2.3771648492623</v>
-      </c>
-      <c r="AF21" s="44">
-        <v>2.3512861736334</v>
-      </c>
-    </row>
-    <row r="22" spans="1:32">
-      <c r="A22" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="B22" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="C22" s="28">
-        <v>2.9553322070354</v>
-      </c>
-      <c r="D22" s="28">
-        <v>2.9820510656337</v>
-      </c>
-      <c r="E22" s="28">
-        <v>3.0466854376556</v>
-      </c>
-      <c r="F22" s="28">
-        <v>2.8813182735974</v>
-      </c>
-      <c r="G22" s="28">
-        <v>2.2109601531893</v>
-      </c>
-      <c r="H22" s="28">
-        <v>2.9772933768118</v>
-      </c>
-      <c r="I22" s="28">
-        <v>2.995695838723</v>
-      </c>
-      <c r="J22" s="28">
-        <v>3.0117556450655</v>
-      </c>
-      <c r="K22" s="28">
-        <v>2.9580646222874</v>
-      </c>
-      <c r="L22" s="28">
-        <v>2.9587614002572</v>
-      </c>
-      <c r="M22" s="28">
-        <v>2.9156195196378</v>
-      </c>
-      <c r="N22" s="28">
-        <v>2.7902165535899</v>
-      </c>
-      <c r="O22" s="28">
-        <v>3.1544844838278</v>
-      </c>
-      <c r="P22" s="28">
-        <v>3.1372607601796</v>
-      </c>
-      <c r="Q22" s="28">
-        <v>3.1584624776661</v>
-      </c>
-      <c r="R22" s="28">
-        <v>3.6188240459995</v>
-      </c>
-      <c r="S22" s="28">
-        <v>3.6315882846847</v>
-      </c>
-      <c r="T22" s="28">
-        <v>3.5458888554717</v>
-      </c>
-      <c r="U22" s="28">
-        <v>2.7553951429907</v>
-      </c>
-      <c r="V22" s="28">
-        <v>3.3518219115298</v>
-      </c>
-      <c r="W22" s="28">
-        <v>2.853340893642</v>
-      </c>
-      <c r="X22" s="28">
-        <v>2.8366732550699</v>
-      </c>
-      <c r="Y22" s="28">
-        <v>2.831604104833</v>
-      </c>
-      <c r="Z22" s="28">
-        <v>2.7627322683109</v>
-      </c>
-      <c r="AA22" s="28">
-        <v>2.8030101516027</v>
-      </c>
-      <c r="AB22" s="28">
-        <v>2.2198538821648</v>
-      </c>
-      <c r="AC22" s="28">
-        <v>3.0428811985329</v>
-      </c>
-      <c r="AD22" s="28">
-        <v>3.0011513275093</v>
-      </c>
-      <c r="AE22" s="28">
-        <v>2.9843223156703</v>
-      </c>
-      <c r="AF22" s="41">
-        <v>4.9433742841649</v>
-      </c>
-    </row>
-    <row r="23" spans="1:32">
-      <c r="A23" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="B23" s="17"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="17"/>
-      <c r="H23" s="17"/>
-      <c r="I23" s="17"/>
-      <c r="J23" s="17"/>
-      <c r="K23" s="17"/>
-      <c r="L23" s="17"/>
-      <c r="M23" s="17"/>
-      <c r="N23" s="17"/>
-      <c r="O23" s="17"/>
-      <c r="P23" s="17"/>
-      <c r="Q23" s="17"/>
-      <c r="R23" s="17"/>
-      <c r="S23" s="17"/>
-      <c r="T23" s="17"/>
-      <c r="U23" s="17"/>
-      <c r="V23" s="17"/>
-      <c r="W23" s="17"/>
-      <c r="X23" s="17"/>
-      <c r="Y23" s="17"/>
-      <c r="Z23" s="17"/>
-      <c r="AA23" s="17"/>
-      <c r="AB23" s="17"/>
-      <c r="AC23" s="17"/>
-      <c r="AD23" s="17"/>
-      <c r="AE23" s="17"/>
-      <c r="AF23" s="42"/>
-    </row>
-    <row r="24" spans="1:32">
-      <c r="A24" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="B24" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="C24" s="24">
         <v>84.450689147598</v>
       </c>
       <c r="D24" s="24">
